--- a/excel_outputs/pglib_opf_case300_ieee.xlsx
+++ b/excel_outputs/pglib_opf_case300_ieee.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\firda\belajar\ISE711\excel_outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5930D40F-223A-4F9E-97C3-14321427D285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833D4D27-4694-4A11-80BC-53C198684F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="baseMVA" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,29 @@
     <sheet name="gencost" sheetId="4" r:id="rId4"/>
     <sheet name="branch" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">bus!$O$2:$T$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">gen!$A$1:$V$70</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="55">
   <si>
     <t>bus_i</t>
   </si>
@@ -184,12 +201,18 @@
   <si>
     <t>line_ID</t>
   </si>
+  <si>
+    <t>infeasible</t>
+  </si>
+  <si>
+    <t>d_new</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,6 +226,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -212,7 +241,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -235,15 +264,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -569,10 +614,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M301"/>
+  <dimension ref="A1:T301"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -612,8 +657,16 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="P1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -653,8 +706,27 @@
       <c r="M2">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O2">
+        <v>-0.9</v>
+      </c>
+      <c r="P2">
+        <v>-0.840028153261139</v>
+      </c>
+      <c r="Q2">
+        <v>-0.77241598029202996</v>
+      </c>
+      <c r="R2">
+        <v>-0.81586728767348404</v>
+      </c>
+      <c r="S2" s="4">
+        <v>0.81586728767348404</v>
+      </c>
+      <c r="T2" t="b">
+        <f>R2=-S2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -694,8 +766,27 @@
       <c r="M3">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O3">
+        <v>-0.56000000000000005</v>
+      </c>
+      <c r="P3">
+        <v>-0.58431473817522595</v>
+      </c>
+      <c r="Q3">
+        <v>-0.51864473927768395</v>
+      </c>
+      <c r="R3">
+        <v>-0.47915002358203501</v>
+      </c>
+      <c r="S3">
+        <v>0.47915002358203501</v>
+      </c>
+      <c r="T3" t="b">
+        <f t="shared" ref="T3:T66" si="0">R3=-S3</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -735,8 +826,27 @@
       <c r="M4">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O4">
+        <v>-0.2</v>
+      </c>
+      <c r="P4">
+        <v>-0.21772071598586201</v>
+      </c>
+      <c r="Q4">
+        <v>-0.18428453950461701</v>
+      </c>
+      <c r="R4">
+        <v>-0.17382104780403301</v>
+      </c>
+      <c r="S4">
+        <v>0.17382104780403301</v>
+      </c>
+      <c r="T4" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -776,8 +886,27 @@
       <c r="M5">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -817,8 +946,27 @@
       <c r="M6">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O6">
+        <v>-3.53</v>
+      </c>
+      <c r="P6">
+        <v>-3.4096902166973</v>
+      </c>
+      <c r="Q6">
+        <v>-3.3044217297310099</v>
+      </c>
+      <c r="R6">
+        <v>-3.34848689648849</v>
+      </c>
+      <c r="S6">
+        <v>3.34848689648849</v>
+      </c>
+      <c r="T6" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -858,8 +1006,27 @@
       <c r="M7">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O7">
+        <v>-1.2</v>
+      </c>
+      <c r="P7">
+        <v>-1.17288483121579</v>
+      </c>
+      <c r="Q7">
+        <v>-1.10550447523315</v>
+      </c>
+      <c r="R7">
+        <v>-1.0526495856804501</v>
+      </c>
+      <c r="S7">
+        <v>1.0526495856804501</v>
+      </c>
+      <c r="T7" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -899,8 +1066,27 @@
       <c r="M8">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -940,8 +1126,27 @@
       <c r="M9">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O9">
+        <v>-0.63</v>
+      </c>
+      <c r="P9">
+        <v>-0.64060707883617396</v>
+      </c>
+      <c r="Q9">
+        <v>-0.59588796013832801</v>
+      </c>
+      <c r="R9">
+        <v>-0.58320752378747298</v>
+      </c>
+      <c r="S9">
+        <v>0.58320752378747298</v>
+      </c>
+      <c r="T9" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -981,8 +1186,27 @@
       <c r="M10">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O10">
+        <v>-0.96</v>
+      </c>
+      <c r="P10">
+        <v>-0.99996202423043501</v>
+      </c>
+      <c r="Q10">
+        <v>-0.836481502353145</v>
+      </c>
+      <c r="R10">
+        <v>-0.82970827466802199</v>
+      </c>
+      <c r="S10">
+        <v>0.82970827466802199</v>
+      </c>
+      <c r="T10" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1022,8 +1246,27 @@
       <c r="M11">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O11">
+        <v>-1.53</v>
+      </c>
+      <c r="P11">
+        <v>-1.6537466611871099</v>
+      </c>
+      <c r="Q11">
+        <v>-1.4091943048478599</v>
+      </c>
+      <c r="R11">
+        <v>-1.35521235496272</v>
+      </c>
+      <c r="S11">
+        <v>1.35521235496272</v>
+      </c>
+      <c r="T11" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1063,8 +1306,27 @@
       <c r="M12">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O12">
+        <v>-0.83</v>
+      </c>
+      <c r="P12">
+        <v>-0.91240059724531997</v>
+      </c>
+      <c r="Q12">
+        <v>-0.80691623493378195</v>
+      </c>
+      <c r="R12">
+        <v>-0.76302763783570704</v>
+      </c>
+      <c r="S12">
+        <v>0.76302763783570704</v>
+      </c>
+      <c r="T12" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1104,8 +1366,27 @@
       <c r="M13">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1145,8 +1426,27 @@
       <c r="M14">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O14">
+        <v>-0.57999999999999996</v>
+      </c>
+      <c r="P14">
+        <v>-0.60319734134438796</v>
+      </c>
+      <c r="Q14">
+        <v>-0.50314747708380803</v>
+      </c>
+      <c r="R14">
+        <v>-0.51035489734700201</v>
+      </c>
+      <c r="S14">
+        <v>0.51035489734700201</v>
+      </c>
+      <c r="T14" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1186,8 +1486,27 @@
       <c r="M15">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O15">
+        <v>-1.6</v>
+      </c>
+      <c r="P15">
+        <v>-1.6169156139574501</v>
+      </c>
+      <c r="Q15">
+        <v>-1.5027888977868999</v>
+      </c>
+      <c r="R15">
+        <v>-1.48900254940674</v>
+      </c>
+      <c r="S15">
+        <v>1.48900254940674</v>
+      </c>
+      <c r="T15" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1227,8 +1546,27 @@
       <c r="M16">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O16">
+        <v>-1.2669999999999999</v>
+      </c>
+      <c r="P16">
+        <v>-1.3707307987178301</v>
+      </c>
+      <c r="Q16">
+        <v>-1.1680495476128601</v>
+      </c>
+      <c r="R16">
+        <v>-1.14209324541404</v>
+      </c>
+      <c r="S16">
+        <v>1.14209324541404</v>
+      </c>
+      <c r="T16" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1268,8 +1606,27 @@
       <c r="M17">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1309,8 +1666,27 @@
       <c r="M18">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O18">
+        <v>-5.61</v>
+      </c>
+      <c r="P18">
+        <v>-5.6024509647956</v>
+      </c>
+      <c r="Q18">
+        <v>-5.4363484988589104</v>
+      </c>
+      <c r="R18">
+        <v>-4.6210914019029703</v>
+      </c>
+      <c r="S18">
+        <v>4.6210914019029703</v>
+      </c>
+      <c r="T18" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>19</v>
       </c>
@@ -1350,8 +1726,27 @@
       <c r="M19">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -1391,8 +1786,27 @@
       <c r="M20">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O20">
+        <v>-6.05</v>
+      </c>
+      <c r="P20">
+        <v>-6.4200022658226299</v>
+      </c>
+      <c r="Q20">
+        <v>-5.77161924978477</v>
+      </c>
+      <c r="R20">
+        <v>-5.5866976932769203</v>
+      </c>
+      <c r="S20">
+        <v>5.5866976932769203</v>
+      </c>
+      <c r="T20" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>21</v>
       </c>
@@ -1432,8 +1846,27 @@
       <c r="M21">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O21">
+        <v>-0.77</v>
+      </c>
+      <c r="P21">
+        <v>-0.79565873437845802</v>
+      </c>
+      <c r="Q21">
+        <v>-0.78887171831538005</v>
+      </c>
+      <c r="R21">
+        <v>-0.68674293559865995</v>
+      </c>
+      <c r="S21">
+        <v>0.68674293559865995</v>
+      </c>
+      <c r="T21" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -1473,8 +1906,27 @@
       <c r="M22">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O22">
+        <v>-0.81</v>
+      </c>
+      <c r="P22">
+        <v>-0.86445534975660299</v>
+      </c>
+      <c r="Q22">
+        <v>-0.72694581577920203</v>
+      </c>
+      <c r="R22">
+        <v>-0.76820774130200498</v>
+      </c>
+      <c r="S22">
+        <v>0.76820774130200498</v>
+      </c>
+      <c r="T22" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>23</v>
       </c>
@@ -1514,8 +1966,27 @@
       <c r="M23">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O23">
+        <v>-0.21</v>
+      </c>
+      <c r="P23">
+        <v>-0.212204720186117</v>
+      </c>
+      <c r="Q23">
+        <v>-0.195467955195717</v>
+      </c>
+      <c r="R23">
+        <v>-0.18456157278836999</v>
+      </c>
+      <c r="S23">
+        <v>0.18456157278836999</v>
+      </c>
+      <c r="T23" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>24</v>
       </c>
@@ -1555,8 +2026,27 @@
       <c r="M24">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25</v>
       </c>
@@ -1596,8 +2086,27 @@
       <c r="M25">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O25">
+        <v>-0.45</v>
+      </c>
+      <c r="P25">
+        <v>-0.478859157620593</v>
+      </c>
+      <c r="Q25">
+        <v>-0.40667423247831103</v>
+      </c>
+      <c r="R25">
+        <v>-0.41004922002032401</v>
+      </c>
+      <c r="S25">
+        <v>0.41004922002032401</v>
+      </c>
+      <c r="T25" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26</v>
       </c>
@@ -1637,8 +2146,27 @@
       <c r="M26">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O26">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="P26">
+        <v>-0.29548550441862997</v>
+      </c>
+      <c r="Q26">
+        <v>-0.24967627731898601</v>
+      </c>
+      <c r="R26">
+        <v>-0.24673803892818599</v>
+      </c>
+      <c r="S26">
+        <v>0.24673803892818599</v>
+      </c>
+      <c r="T26" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>27</v>
       </c>
@@ -1678,8 +2206,27 @@
       <c r="M27">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O27">
+        <v>-0.69</v>
+      </c>
+      <c r="P27">
+        <v>-0.75398015448817002</v>
+      </c>
+      <c r="Q27">
+        <v>-0.64382663605978796</v>
+      </c>
+      <c r="R27">
+        <v>-0.62585102300826401</v>
+      </c>
+      <c r="S27">
+        <v>0.62585102300826401</v>
+      </c>
+      <c r="T27" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>33</v>
       </c>
@@ -1719,8 +2266,27 @@
       <c r="M28">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O28">
+        <v>-0.55000000000000004</v>
+      </c>
+      <c r="P28">
+        <v>-0.56228763382678904</v>
+      </c>
+      <c r="Q28">
+        <v>-0.49332620242746</v>
+      </c>
+      <c r="R28">
+        <v>-0.475466814317825</v>
+      </c>
+      <c r="S28">
+        <v>0.475466814317825</v>
+      </c>
+      <c r="T28" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>34</v>
       </c>
@@ -1760,8 +2326,27 @@
       <c r="M29">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>35</v>
       </c>
@@ -1801,8 +2386,27 @@
       <c r="M30">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>36</v>
       </c>
@@ -1842,8 +2446,27 @@
       <c r="M31">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>37</v>
       </c>
@@ -1883,8 +2506,27 @@
       <c r="M32">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O32">
+        <v>-0.85</v>
+      </c>
+      <c r="P32">
+        <v>-0.93011977010590197</v>
+      </c>
+      <c r="Q32">
+        <v>-0.83114340245818497</v>
+      </c>
+      <c r="R32">
+        <v>-0.71325906652848903</v>
+      </c>
+      <c r="S32">
+        <v>0.71325906652848903</v>
+      </c>
+      <c r="T32" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>38</v>
       </c>
@@ -1924,8 +2566,27 @@
       <c r="M33">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O33">
+        <v>-1.55</v>
+      </c>
+      <c r="P33">
+        <v>-1.72458828901822</v>
+      </c>
+      <c r="Q33">
+        <v>-1.5245529326818501</v>
+      </c>
+      <c r="R33">
+        <v>-1.4747724872032899</v>
+      </c>
+      <c r="S33">
+        <v>1.4747724872032899</v>
+      </c>
+      <c r="T33" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>39</v>
       </c>
@@ -1965,8 +2626,27 @@
       <c r="M34">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>40</v>
       </c>
@@ -2006,8 +2686,27 @@
       <c r="M35">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O35">
+        <v>-0.46</v>
+      </c>
+      <c r="P35">
+        <v>-0.48575993228845599</v>
+      </c>
+      <c r="Q35">
+        <v>-0.41103399608206198</v>
+      </c>
+      <c r="R35">
+        <v>-0.40830157549028401</v>
+      </c>
+      <c r="S35">
+        <v>0.40830157549028401</v>
+      </c>
+      <c r="T35" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>41</v>
       </c>
@@ -2047,8 +2746,27 @@
       <c r="M36">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O36">
+        <v>-0.86</v>
+      </c>
+      <c r="P36">
+        <v>-0.85739567347400003</v>
+      </c>
+      <c r="Q36">
+        <v>-0.78522654598908603</v>
+      </c>
+      <c r="R36">
+        <v>-0.76753550285198302</v>
+      </c>
+      <c r="S36">
+        <v>0.76753550285198302</v>
+      </c>
+      <c r="T36" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>42</v>
       </c>
@@ -2088,8 +2806,27 @@
       <c r="M37">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>43</v>
       </c>
@@ -2129,8 +2866,27 @@
       <c r="M38">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O38">
+        <v>-0.39</v>
+      </c>
+      <c r="P38">
+        <v>-0.42528670514288502</v>
+      </c>
+      <c r="Q38">
+        <v>-0.36877844785050801</v>
+      </c>
+      <c r="R38">
+        <v>-0.34555799007786198</v>
+      </c>
+      <c r="S38">
+        <v>0.34555799007786198</v>
+      </c>
+      <c r="T38" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>44</v>
       </c>
@@ -2170,8 +2926,27 @@
       <c r="M39">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O39">
+        <v>-1.95</v>
+      </c>
+      <c r="P39">
+        <v>-2.11405431878251</v>
+      </c>
+      <c r="Q39">
+        <v>-1.83905152486604</v>
+      </c>
+      <c r="R39">
+        <v>-1.61003514780739</v>
+      </c>
+      <c r="S39">
+        <v>1.61003514780739</v>
+      </c>
+      <c r="T39" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>45</v>
       </c>
@@ -2211,8 +2986,27 @@
       <c r="M40">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>46</v>
       </c>
@@ -2252,8 +3046,27 @@
       <c r="M41">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>47</v>
       </c>
@@ -2293,8 +3106,27 @@
       <c r="M42">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O42">
+        <v>-0.57999999999999996</v>
+      </c>
+      <c r="P42">
+        <v>-0.57353567853043796</v>
+      </c>
+      <c r="Q42">
+        <v>-0.55944552671994896</v>
+      </c>
+      <c r="R42">
+        <v>-0.49377498776616102</v>
+      </c>
+      <c r="S42">
+        <v>0.49377498776616102</v>
+      </c>
+      <c r="T42" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>48</v>
       </c>
@@ -2334,8 +3166,27 @@
       <c r="M43">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O43">
+        <v>-0.41</v>
+      </c>
+      <c r="P43">
+        <v>-0.42358121565398599</v>
+      </c>
+      <c r="Q43">
+        <v>-0.38649259560212201</v>
+      </c>
+      <c r="R43">
+        <v>-0.35279833225922602</v>
+      </c>
+      <c r="S43">
+        <v>0.35279833225922602</v>
+      </c>
+      <c r="T43" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>49</v>
       </c>
@@ -2375,8 +3226,27 @@
       <c r="M44">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O44">
+        <v>-0.92</v>
+      </c>
+      <c r="P44">
+        <v>-0.92036390384794897</v>
+      </c>
+      <c r="Q44">
+        <v>-0.93594643518119702</v>
+      </c>
+      <c r="R44">
+        <v>-0.77297681548455899</v>
+      </c>
+      <c r="S44">
+        <v>0.77297681548455899</v>
+      </c>
+      <c r="T44" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>51</v>
       </c>
@@ -2416,8 +3286,27 @@
       <c r="M45">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O45">
+        <v>0.05</v>
+      </c>
+      <c r="P45">
+        <v>4.5765428140611901E-2</v>
+      </c>
+      <c r="Q45">
+        <v>4.74274768074796E-2</v>
+      </c>
+      <c r="R45">
+        <v>4.2942290336241001E-2</v>
+      </c>
+      <c r="S45">
+        <v>-4.2942290336241001E-2</v>
+      </c>
+      <c r="T45" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>52</v>
       </c>
@@ -2457,8 +3346,27 @@
       <c r="M46">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O46">
+        <v>-0.61</v>
+      </c>
+      <c r="P46">
+        <v>-0.66920149260119599</v>
+      </c>
+      <c r="Q46">
+        <v>-0.53275759787846</v>
+      </c>
+      <c r="R46">
+        <v>-0.54563364642991596</v>
+      </c>
+      <c r="S46">
+        <v>0.54563364642991596</v>
+      </c>
+      <c r="T46" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>53</v>
       </c>
@@ -2498,8 +3406,27 @@
       <c r="M47">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O47">
+        <v>-0.69</v>
+      </c>
+      <c r="P47">
+        <v>-0.76621116665602995</v>
+      </c>
+      <c r="Q47">
+        <v>-0.65948277114377796</v>
+      </c>
+      <c r="R47">
+        <v>-0.59946881855476397</v>
+      </c>
+      <c r="S47">
+        <v>0.59946881855476397</v>
+      </c>
+      <c r="T47" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>54</v>
       </c>
@@ -2539,8 +3466,27 @@
       <c r="M48">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O48">
+        <v>-0.1</v>
+      </c>
+      <c r="P48">
+        <v>-0.103302527211923</v>
+      </c>
+      <c r="Q48">
+        <v>-9.0987111386241007E-2</v>
+      </c>
+      <c r="R48">
+        <v>-8.3545760708822595E-2</v>
+      </c>
+      <c r="S48">
+        <v>8.3545760708822595E-2</v>
+      </c>
+      <c r="T48" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>55</v>
       </c>
@@ -2580,8 +3526,27 @@
       <c r="M49">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O49">
+        <v>-0.22</v>
+      </c>
+      <c r="P49">
+        <v>-0.23346801020119201</v>
+      </c>
+      <c r="Q49">
+        <v>-0.20162277260987599</v>
+      </c>
+      <c r="R49">
+        <v>-0.181602085254012</v>
+      </c>
+      <c r="S49">
+        <v>0.181602085254012</v>
+      </c>
+      <c r="T49" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>57</v>
       </c>
@@ -2621,8 +3586,27 @@
       <c r="M50">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O50">
+        <v>-0.98</v>
+      </c>
+      <c r="P50">
+        <v>-1.0472229402950199</v>
+      </c>
+      <c r="Q50">
+        <v>-0.91150269980157095</v>
+      </c>
+      <c r="R50">
+        <v>-0.898463522550213</v>
+      </c>
+      <c r="S50">
+        <v>0.898463522550213</v>
+      </c>
+      <c r="T50" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>58</v>
       </c>
@@ -2662,8 +3646,27 @@
       <c r="M51">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O51">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="P51">
+        <v>-0.13447721243653099</v>
+      </c>
+      <c r="Q51">
+        <v>-0.123613423300204</v>
+      </c>
+      <c r="R51">
+        <v>-0.12304269434188</v>
+      </c>
+      <c r="S51">
+        <v>0.12304269434188</v>
+      </c>
+      <c r="T51" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>59</v>
       </c>
@@ -2703,8 +3706,27 @@
       <c r="M52">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O52">
+        <v>-2.1800000000000002</v>
+      </c>
+      <c r="P52">
+        <v>-2.24573489227584</v>
+      </c>
+      <c r="Q52">
+        <v>-2.0853859343806298</v>
+      </c>
+      <c r="R52">
+        <v>-1.8787310807995801</v>
+      </c>
+      <c r="S52">
+        <v>1.8787310807995801</v>
+      </c>
+      <c r="T52" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>60</v>
       </c>
@@ -2744,8 +3766,27 @@
       <c r="M53">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>61</v>
       </c>
@@ -2785,8 +3826,27 @@
       <c r="M54">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O54">
+        <v>-2.27</v>
+      </c>
+      <c r="P54">
+        <v>-2.3057685821846401</v>
+      </c>
+      <c r="Q54">
+        <v>-2.1334841934264799</v>
+      </c>
+      <c r="R54">
+        <v>-2.0077472874976201</v>
+      </c>
+      <c r="S54">
+        <v>2.0077472874976201</v>
+      </c>
+      <c r="T54" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>62</v>
       </c>
@@ -2826,8 +3886,27 @@
       <c r="M55">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>63</v>
       </c>
@@ -2867,8 +3946,27 @@
       <c r="M56">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O56">
+        <v>-0.7</v>
+      </c>
+      <c r="P56">
+        <v>-0.70945447413164098</v>
+      </c>
+      <c r="Q56">
+        <v>-0.65986661917690703</v>
+      </c>
+      <c r="R56">
+        <v>-0.58614469364266697</v>
+      </c>
+      <c r="S56">
+        <v>0.58614469364266697</v>
+      </c>
+      <c r="T56" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>64</v>
       </c>
@@ -2908,8 +4006,27 @@
       <c r="M57">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>69</v>
       </c>
@@ -2949,8 +4066,27 @@
       <c r="M58">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>70</v>
       </c>
@@ -2990,8 +4126,27 @@
       <c r="M59">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O59">
+        <v>-0.56000000000000005</v>
+      </c>
+      <c r="P59">
+        <v>-0.66508179883836704</v>
+      </c>
+      <c r="Q59">
+        <v>-0.50653828546271695</v>
+      </c>
+      <c r="R59">
+        <v>-0.51091707615326298</v>
+      </c>
+      <c r="S59">
+        <v>0.51091707615326298</v>
+      </c>
+      <c r="T59" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>71</v>
       </c>
@@ -3031,8 +4186,27 @@
       <c r="M60">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O60">
+        <v>-1.1599999999999999</v>
+      </c>
+      <c r="P60">
+        <v>-1.1590215074914001</v>
+      </c>
+      <c r="Q60">
+        <v>-1.0779637894126499</v>
+      </c>
+      <c r="R60">
+        <v>-1.0110079460014101</v>
+      </c>
+      <c r="S60">
+        <v>1.0110079460014101</v>
+      </c>
+      <c r="T60" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>72</v>
       </c>
@@ -3072,8 +4246,27 @@
       <c r="M61">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O61">
+        <v>-0.56999999999999995</v>
+      </c>
+      <c r="P61">
+        <v>-0.58154534107484901</v>
+      </c>
+      <c r="Q61">
+        <v>-0.49280227603437998</v>
+      </c>
+      <c r="R61">
+        <v>-0.468784010126026</v>
+      </c>
+      <c r="S61">
+        <v>0.468784010126026</v>
+      </c>
+      <c r="T61" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>73</v>
       </c>
@@ -3113,8 +4306,27 @@
       <c r="M62">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O62">
+        <v>-2.2400000000000002</v>
+      </c>
+      <c r="P62">
+        <v>-2.31772601520841</v>
+      </c>
+      <c r="Q62">
+        <v>-2.0204608899574499</v>
+      </c>
+      <c r="R62">
+        <v>-2.0136060396704298</v>
+      </c>
+      <c r="S62">
+        <v>2.0136060396704298</v>
+      </c>
+      <c r="T62" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>74</v>
       </c>
@@ -3154,8 +4366,27 @@
       <c r="M63">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>76</v>
       </c>
@@ -3195,8 +4426,27 @@
       <c r="M64">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O64">
+        <v>-2.08</v>
+      </c>
+      <c r="P64">
+        <v>-1.9268330868792201</v>
+      </c>
+      <c r="Q64">
+        <v>-1.8355069399244099</v>
+      </c>
+      <c r="R64">
+        <v>-1.86184512279685</v>
+      </c>
+      <c r="S64">
+        <v>1.86184512279685</v>
+      </c>
+      <c r="T64" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>77</v>
       </c>
@@ -3236,8 +4486,27 @@
       <c r="M65">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O65">
+        <v>-0.74</v>
+      </c>
+      <c r="P65">
+        <v>-0.76472570196137302</v>
+      </c>
+      <c r="Q65">
+        <v>-0.65927327735276398</v>
+      </c>
+      <c r="R65">
+        <v>-0.63783295854418698</v>
+      </c>
+      <c r="S65">
+        <v>0.63783295854418698</v>
+      </c>
+      <c r="T65" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>78</v>
       </c>
@@ -3277,8 +4546,27 @@
       <c r="M66">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>79</v>
       </c>
@@ -3318,8 +4606,27 @@
       <c r="M67">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O67">
+        <v>-0.48</v>
+      </c>
+      <c r="P67">
+        <v>-0.49074029039737899</v>
+      </c>
+      <c r="Q67">
+        <v>-0.43596227451916097</v>
+      </c>
+      <c r="R67">
+        <v>-0.441728235732885</v>
+      </c>
+      <c r="S67">
+        <v>0.441728235732885</v>
+      </c>
+      <c r="T67" t="b">
+        <f t="shared" ref="T67:T130" si="1">R67=-S67</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>80</v>
       </c>
@@ -3359,8 +4666,27 @@
       <c r="M68">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O68">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="P68">
+        <v>-0.287977773296134</v>
+      </c>
+      <c r="Q68">
+        <v>-0.26405263466970702</v>
+      </c>
+      <c r="R68">
+        <v>-0.247063881944668</v>
+      </c>
+      <c r="S68">
+        <v>0.247063881944668</v>
+      </c>
+      <c r="T68" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>81</v>
       </c>
@@ -3400,8 +4726,27 @@
       <c r="M69">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>84</v>
       </c>
@@ -3441,8 +4786,27 @@
       <c r="M70">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O70">
+        <v>-0.37</v>
+      </c>
+      <c r="P70">
+        <v>-0.35964263696488502</v>
+      </c>
+      <c r="Q70">
+        <v>-0.34603608296906901</v>
+      </c>
+      <c r="R70">
+        <v>-0.32803209442171399</v>
+      </c>
+      <c r="S70">
+        <v>0.32803209442171399</v>
+      </c>
+      <c r="T70" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>85</v>
       </c>
@@ -3482,8 +4846,27 @@
       <c r="M71">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="T71" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>86</v>
       </c>
@@ -3523,8 +4906,27 @@
       <c r="M72">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="T72" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>87</v>
       </c>
@@ -3564,8 +4966,27 @@
       <c r="M73">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>0</v>
+      </c>
+      <c r="T73" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>88</v>
       </c>
@@ -3605,8 +5026,27 @@
       <c r="M74">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="T74" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>89</v>
       </c>
@@ -3646,8 +5086,27 @@
       <c r="M75">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O75">
+        <v>-0.442</v>
+      </c>
+      <c r="P75">
+        <v>-0.438491443550386</v>
+      </c>
+      <c r="Q75">
+        <v>-0.405763597010669</v>
+      </c>
+      <c r="R75">
+        <v>-0.39958984145112297</v>
+      </c>
+      <c r="S75">
+        <v>0.39958984145112297</v>
+      </c>
+      <c r="T75" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>90</v>
       </c>
@@ -3687,8 +5146,27 @@
       <c r="M76">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O76">
+        <v>-0.66</v>
+      </c>
+      <c r="P76">
+        <v>-0.75763158571503897</v>
+      </c>
+      <c r="Q76">
+        <v>-0.63190419916993401</v>
+      </c>
+      <c r="R76">
+        <v>-0.67783921230993005</v>
+      </c>
+      <c r="S76">
+        <v>0.67783921230993005</v>
+      </c>
+      <c r="T76" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>91</v>
       </c>
@@ -3728,8 +5206,27 @@
       <c r="M77">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O77">
+        <v>-0.17399999999999999</v>
+      </c>
+      <c r="P77">
+        <v>-0.18034444715973</v>
+      </c>
+      <c r="Q77">
+        <v>-0.16120860663282499</v>
+      </c>
+      <c r="R77">
+        <v>-0.16305653557937599</v>
+      </c>
+      <c r="S77">
+        <v>0.16305653557937599</v>
+      </c>
+      <c r="T77" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>92</v>
       </c>
@@ -3769,8 +5266,27 @@
       <c r="M78">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O78">
+        <v>-0.158</v>
+      </c>
+      <c r="P78">
+        <v>-0.169669233829008</v>
+      </c>
+      <c r="Q78">
+        <v>-0.153364561665673</v>
+      </c>
+      <c r="R78">
+        <v>-0.146699721425228</v>
+      </c>
+      <c r="S78">
+        <v>0.146699721425228</v>
+      </c>
+      <c r="T78" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>94</v>
       </c>
@@ -3810,8 +5326,27 @@
       <c r="M79">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O79">
+        <v>-0.60299999999999998</v>
+      </c>
+      <c r="P79">
+        <v>-0.568575972478358</v>
+      </c>
+      <c r="Q79">
+        <v>-0.53204259912067997</v>
+      </c>
+      <c r="R79">
+        <v>-0.525031940044969</v>
+      </c>
+      <c r="S79">
+        <v>0.525031940044969</v>
+      </c>
+      <c r="T79" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>97</v>
       </c>
@@ -3851,8 +5386,27 @@
       <c r="M80">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O80">
+        <v>-0.39899999999999902</v>
+      </c>
+      <c r="P80">
+        <v>-0.40677919733245799</v>
+      </c>
+      <c r="Q80">
+        <v>-0.39348283789605998</v>
+      </c>
+      <c r="R80">
+        <v>-0.358546709858104</v>
+      </c>
+      <c r="S80">
+        <v>0.358546709858104</v>
+      </c>
+      <c r="T80" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>98</v>
       </c>
@@ -3892,8 +5446,27 @@
       <c r="M81">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O81">
+        <v>-0.66700000000000004</v>
+      </c>
+      <c r="P81">
+        <v>-0.65263788871714201</v>
+      </c>
+      <c r="Q81">
+        <v>-0.56300100926451302</v>
+      </c>
+      <c r="R81">
+        <v>-0.58427439951017601</v>
+      </c>
+      <c r="S81">
+        <v>0.58427439951017601</v>
+      </c>
+      <c r="T81" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>99</v>
       </c>
@@ -3933,8 +5506,27 @@
       <c r="M82">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O82">
+        <v>-0.83499999999999996</v>
+      </c>
+      <c r="P82">
+        <v>-0.81157449744680998</v>
+      </c>
+      <c r="Q82">
+        <v>-0.80168952510985603</v>
+      </c>
+      <c r="R82">
+        <v>-0.73030365293871202</v>
+      </c>
+      <c r="S82">
+        <v>0.73030365293871202</v>
+      </c>
+      <c r="T82" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>100</v>
       </c>
@@ -3974,8 +5566,27 @@
       <c r="M83">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>0</v>
+      </c>
+      <c r="R83">
+        <v>0</v>
+      </c>
+      <c r="S83">
+        <v>0</v>
+      </c>
+      <c r="T83" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>102</v>
       </c>
@@ -4015,8 +5626,27 @@
       <c r="M84">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O84">
+        <v>-0.77800000000000002</v>
+      </c>
+      <c r="P84">
+        <v>-0.76143720740646603</v>
+      </c>
+      <c r="Q84">
+        <v>-0.78348169365250897</v>
+      </c>
+      <c r="R84">
+        <v>-0.65759268720635</v>
+      </c>
+      <c r="S84">
+        <v>0.65759268720635</v>
+      </c>
+      <c r="T84" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>103</v>
       </c>
@@ -4056,8 +5686,27 @@
       <c r="M85">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O85">
+        <v>-0.32</v>
+      </c>
+      <c r="P85">
+        <v>-0.32736052316405301</v>
+      </c>
+      <c r="Q85">
+        <v>-0.30989408740850499</v>
+      </c>
+      <c r="R85">
+        <v>-0.29956218444750998</v>
+      </c>
+      <c r="S85">
+        <v>0.29956218444750998</v>
+      </c>
+      <c r="T85" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>104</v>
       </c>
@@ -4097,8 +5746,27 @@
       <c r="M86">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O86">
+        <v>-8.5999999999999993E-2</v>
+      </c>
+      <c r="P86">
+        <v>-9.3055015937555996E-2</v>
+      </c>
+      <c r="Q86">
+        <v>-7.8441742274505399E-2</v>
+      </c>
+      <c r="R86">
+        <v>-7.1435093646546294E-2</v>
+      </c>
+      <c r="S86">
+        <v>7.1435093646546294E-2</v>
+      </c>
+      <c r="T86" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>105</v>
       </c>
@@ -4138,8 +5806,27 @@
       <c r="M87">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O87">
+        <v>-0.496</v>
+      </c>
+      <c r="P87">
+        <v>-0.54295594591436303</v>
+      </c>
+      <c r="Q87">
+        <v>-0.43760296819670003</v>
+      </c>
+      <c r="R87">
+        <v>-0.43031663412932197</v>
+      </c>
+      <c r="S87">
+        <v>0.43031663412932197</v>
+      </c>
+      <c r="T87" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>107</v>
       </c>
@@ -4179,8 +5866,27 @@
       <c r="M88">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O88">
+        <v>-4.5999999999999999E-2</v>
+      </c>
+      <c r="P88">
+        <v>-5.1555972005673301E-2</v>
+      </c>
+      <c r="Q88">
+        <v>-4.0912029062177203E-2</v>
+      </c>
+      <c r="R88">
+        <v>-3.8858504355931002E-2</v>
+      </c>
+      <c r="S88">
+        <v>3.8858504355931002E-2</v>
+      </c>
+      <c r="T88" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>108</v>
       </c>
@@ -4220,8 +5926,27 @@
       <c r="M89">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O89">
+        <v>-1.121</v>
+      </c>
+      <c r="P89">
+        <v>-1.24208512958654</v>
+      </c>
+      <c r="Q89">
+        <v>-1.1128036020137899</v>
+      </c>
+      <c r="R89">
+        <v>-0.93305840302780796</v>
+      </c>
+      <c r="S89">
+        <v>0.93305840302780796</v>
+      </c>
+      <c r="T89" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>109</v>
       </c>
@@ -4261,8 +5986,27 @@
       <c r="M90">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O90">
+        <v>-0.307</v>
+      </c>
+      <c r="P90">
+        <v>-0.32477121347990201</v>
+      </c>
+      <c r="Q90">
+        <v>-0.29572655936348802</v>
+      </c>
+      <c r="R90">
+        <v>-0.26775362430668698</v>
+      </c>
+      <c r="S90">
+        <v>0.26775362430668698</v>
+      </c>
+      <c r="T90" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>110</v>
       </c>
@@ -4302,8 +6046,27 @@
       <c r="M91">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O91">
+        <v>-0.63</v>
+      </c>
+      <c r="P91">
+        <v>-0.65422438418610096</v>
+      </c>
+      <c r="Q91">
+        <v>-0.58955403600093803</v>
+      </c>
+      <c r="R91">
+        <v>-0.54278841888673601</v>
+      </c>
+      <c r="S91">
+        <v>0.54278841888673601</v>
+      </c>
+      <c r="T91" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>112</v>
       </c>
@@ -4343,8 +6106,27 @@
       <c r="M92">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O92">
+        <v>-0.19600000000000001</v>
+      </c>
+      <c r="P92">
+        <v>-0.207512952427504</v>
+      </c>
+      <c r="Q92">
+        <v>-0.17199695820980601</v>
+      </c>
+      <c r="R92">
+        <v>-0.18129055963229099</v>
+      </c>
+      <c r="S92">
+        <v>0.18129055963229099</v>
+      </c>
+      <c r="T92" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>113</v>
       </c>
@@ -4384,8 +6166,27 @@
       <c r="M93">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O93">
+        <v>-0.26200000000000001</v>
+      </c>
+      <c r="P93">
+        <v>-0.27866438491163298</v>
+      </c>
+      <c r="Q93">
+        <v>-0.23879969769929299</v>
+      </c>
+      <c r="R93">
+        <v>-0.27178817818724799</v>
+      </c>
+      <c r="S93">
+        <v>0.27178817818724799</v>
+      </c>
+      <c r="T93" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>114</v>
       </c>
@@ -4425,8 +6226,27 @@
       <c r="M94">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O94">
+        <v>-0.182</v>
+      </c>
+      <c r="P94">
+        <v>-0.17310621948781099</v>
+      </c>
+      <c r="Q94">
+        <v>-0.174821708579429</v>
+      </c>
+      <c r="R94">
+        <v>-0.16998000958571799</v>
+      </c>
+      <c r="S94">
+        <v>0.16998000958571799</v>
+      </c>
+      <c r="T94" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>115</v>
       </c>
@@ -4466,8 +6286,27 @@
       <c r="M95">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>0</v>
+      </c>
+      <c r="R95">
+        <v>0</v>
+      </c>
+      <c r="S95">
+        <v>0</v>
+      </c>
+      <c r="T95" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>116</v>
       </c>
@@ -4507,8 +6346,27 @@
       <c r="M96">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>0</v>
+      </c>
+      <c r="R96">
+        <v>0</v>
+      </c>
+      <c r="S96">
+        <v>0</v>
+      </c>
+      <c r="T96" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>117</v>
       </c>
@@ -4548,8 +6406,27 @@
       <c r="M97">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>0</v>
+      </c>
+      <c r="R97">
+        <v>0</v>
+      </c>
+      <c r="S97">
+        <v>0</v>
+      </c>
+      <c r="T97" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>118</v>
       </c>
@@ -4589,8 +6466,27 @@
       <c r="M98">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O98">
+        <v>-0.14099999999999999</v>
+      </c>
+      <c r="P98">
+        <v>-0.14785248394061201</v>
+      </c>
+      <c r="Q98">
+        <v>-0.12624819219457001</v>
+      </c>
+      <c r="R98">
+        <v>-0.13140886529401699</v>
+      </c>
+      <c r="S98">
+        <v>0.13140886529401699</v>
+      </c>
+      <c r="T98" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>119</v>
       </c>
@@ -4630,8 +6526,27 @@
       <c r="M99">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
+        <v>0</v>
+      </c>
+      <c r="R99">
+        <v>0</v>
+      </c>
+      <c r="S99">
+        <v>0</v>
+      </c>
+      <c r="T99" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>120</v>
       </c>
@@ -4671,8 +6586,27 @@
       <c r="M100">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O100">
+        <v>-7.77</v>
+      </c>
+      <c r="P100">
+        <v>-7.7927830873534303</v>
+      </c>
+      <c r="Q100">
+        <v>-7.28757903800365</v>
+      </c>
+      <c r="R100">
+        <v>-6.5934211657055002</v>
+      </c>
+      <c r="S100">
+        <v>6.5934211657055002</v>
+      </c>
+      <c r="T100" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>121</v>
       </c>
@@ -4712,8 +6646,27 @@
       <c r="M101">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O101">
+        <v>-5.35</v>
+      </c>
+      <c r="P101">
+        <v>-5.4110164872507598</v>
+      </c>
+      <c r="Q101">
+        <v>-5.6463041095360298</v>
+      </c>
+      <c r="R101">
+        <v>-4.9724932299466298</v>
+      </c>
+      <c r="S101">
+        <v>4.9724932299466298</v>
+      </c>
+      <c r="T101" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>122</v>
       </c>
@@ -4753,8 +6706,27 @@
       <c r="M102">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O102">
+        <v>-2.2909999999999999</v>
+      </c>
+      <c r="P102">
+        <v>-2.2561426683893799</v>
+      </c>
+      <c r="Q102">
+        <v>-2.1690593029784102</v>
+      </c>
+      <c r="R102">
+        <v>-2.1499917754872802</v>
+      </c>
+      <c r="S102">
+        <v>2.1499917754872802</v>
+      </c>
+      <c r="T102" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>123</v>
       </c>
@@ -4794,8 +6766,27 @@
       <c r="M103">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O103">
+        <v>-0.78</v>
+      </c>
+      <c r="P103">
+        <v>-0.83578285256928397</v>
+      </c>
+      <c r="Q103">
+        <v>-0.73791777359973398</v>
+      </c>
+      <c r="R103">
+        <v>-0.67097750533415301</v>
+      </c>
+      <c r="S103">
+        <v>0.67097750533415301</v>
+      </c>
+      <c r="T103" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>124</v>
       </c>
@@ -4835,8 +6826,27 @@
       <c r="M104">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O104">
+        <v>-2.7639999999999998</v>
+      </c>
+      <c r="P104">
+        <v>-2.8494395832171602</v>
+      </c>
+      <c r="Q104">
+        <v>-2.7358171025944702</v>
+      </c>
+      <c r="R104">
+        <v>-2.5344759386846101</v>
+      </c>
+      <c r="S104">
+        <v>2.5344759386846101</v>
+      </c>
+      <c r="T104" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>125</v>
       </c>
@@ -4876,8 +6886,27 @@
       <c r="M105">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O105">
+        <v>-5.1479999999999997</v>
+      </c>
+      <c r="P105">
+        <v>-5.7056967800912801</v>
+      </c>
+      <c r="Q105">
+        <v>-4.9919851821724501</v>
+      </c>
+      <c r="R105">
+        <v>-4.5970647661431796</v>
+      </c>
+      <c r="S105">
+        <v>4.5970647661431796</v>
+      </c>
+      <c r="T105" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>126</v>
       </c>
@@ -4917,8 +6946,27 @@
       <c r="M106">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O106">
+        <v>-0.57899999999999996</v>
+      </c>
+      <c r="P106">
+        <v>-0.56237886953640004</v>
+      </c>
+      <c r="Q106">
+        <v>-0.50227033591116199</v>
+      </c>
+      <c r="R106">
+        <v>-0.49615286129533998</v>
+      </c>
+      <c r="S106">
+        <v>0.49615286129533998</v>
+      </c>
+      <c r="T106" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>127</v>
       </c>
@@ -4958,8 +7006,27 @@
       <c r="M107">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O107">
+        <v>-3.8079999999999998</v>
+      </c>
+      <c r="P107">
+        <v>-3.72563036108125</v>
+      </c>
+      <c r="Q107">
+        <v>-3.5800498180287299</v>
+      </c>
+      <c r="R107">
+        <v>-3.4331938244818301</v>
+      </c>
+      <c r="S107">
+        <v>3.4331938244818301</v>
+      </c>
+      <c r="T107" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>128</v>
       </c>
@@ -4999,8 +7066,27 @@
       <c r="M108">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+      <c r="Q108">
+        <v>0</v>
+      </c>
+      <c r="R108">
+        <v>0</v>
+      </c>
+      <c r="S108">
+        <v>0</v>
+      </c>
+      <c r="T108" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>129</v>
       </c>
@@ -5040,8 +7126,27 @@
       <c r="M109">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>0</v>
+      </c>
+      <c r="R109">
+        <v>0</v>
+      </c>
+      <c r="S109">
+        <v>0</v>
+      </c>
+      <c r="T109" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>130</v>
       </c>
@@ -5081,8 +7186,27 @@
       <c r="M110">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+      <c r="Q110">
+        <v>0</v>
+      </c>
+      <c r="R110">
+        <v>0</v>
+      </c>
+      <c r="S110">
+        <v>0</v>
+      </c>
+      <c r="T110" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>131</v>
       </c>
@@ -5122,8 +7246,27 @@
       <c r="M111">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>0</v>
+      </c>
+      <c r="R111">
+        <v>0</v>
+      </c>
+      <c r="S111">
+        <v>0</v>
+      </c>
+      <c r="T111" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>132</v>
       </c>
@@ -5163,8 +7306,27 @@
       <c r="M112">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Q112">
+        <v>0</v>
+      </c>
+      <c r="R112">
+        <v>0</v>
+      </c>
+      <c r="S112">
+        <v>0</v>
+      </c>
+      <c r="T112" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>133</v>
       </c>
@@ -5204,8 +7366,27 @@
       <c r="M113">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>0</v>
+      </c>
+      <c r="Q113">
+        <v>0</v>
+      </c>
+      <c r="R113">
+        <v>0</v>
+      </c>
+      <c r="S113">
+        <v>0</v>
+      </c>
+      <c r="T113" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>134</v>
       </c>
@@ -5245,8 +7426,27 @@
       <c r="M114">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+      <c r="Q114">
+        <v>0</v>
+      </c>
+      <c r="R114">
+        <v>0</v>
+      </c>
+      <c r="S114">
+        <v>0</v>
+      </c>
+      <c r="T114" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>135</v>
       </c>
@@ -5286,8 +7486,27 @@
       <c r="M115">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O115">
+        <v>-1.6919999999999999</v>
+      </c>
+      <c r="P115">
+        <v>-1.5901649392806201</v>
+      </c>
+      <c r="Q115">
+        <v>-1.5748885777895401</v>
+      </c>
+      <c r="R115">
+        <v>-1.55155736332165</v>
+      </c>
+      <c r="S115">
+        <v>1.55155736332165</v>
+      </c>
+      <c r="T115" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>136</v>
       </c>
@@ -5327,8 +7546,27 @@
       <c r="M116">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O116">
+        <v>-0.55200000000000005</v>
+      </c>
+      <c r="P116">
+        <v>-0.54686191512068905</v>
+      </c>
+      <c r="Q116">
+        <v>-0.49295053028944402</v>
+      </c>
+      <c r="R116">
+        <v>-0.47279190267987498</v>
+      </c>
+      <c r="S116">
+        <v>0.47279190267987498</v>
+      </c>
+      <c r="T116" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>137</v>
       </c>
@@ -5368,8 +7606,27 @@
       <c r="M117">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O117">
+        <v>-2.7360000000000002</v>
+      </c>
+      <c r="P117">
+        <v>-2.6745003072982598</v>
+      </c>
+      <c r="Q117">
+        <v>-2.6745896151025299</v>
+      </c>
+      <c r="R117">
+        <v>-2.4682299370246299</v>
+      </c>
+      <c r="S117">
+        <v>2.4682299370246299</v>
+      </c>
+      <c r="T117" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>138</v>
       </c>
@@ -5409,8 +7666,27 @@
       <c r="M118">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O118">
+        <v>-10.192</v>
+      </c>
+      <c r="P118">
+        <v>-10.589769779793301</v>
+      </c>
+      <c r="Q118">
+        <v>-10.545252766011201</v>
+      </c>
+      <c r="R118">
+        <v>-9.3229249724569403</v>
+      </c>
+      <c r="S118">
+        <v>9.3229249724569403</v>
+      </c>
+      <c r="T118" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>139</v>
       </c>
@@ -5450,8 +7726,27 @@
       <c r="M119">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O119">
+        <v>-5.95</v>
+      </c>
+      <c r="P119">
+        <v>-5.5985777799134704</v>
+      </c>
+      <c r="Q119">
+        <v>-5.0317753026837497</v>
+      </c>
+      <c r="R119">
+        <v>-5.5953183356824203</v>
+      </c>
+      <c r="S119">
+        <v>5.5953183356824203</v>
+      </c>
+      <c r="T119" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>140</v>
       </c>
@@ -5491,8 +7786,27 @@
       <c r="M120">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O120">
+        <v>-3.8769999999999998</v>
+      </c>
+      <c r="P120">
+        <v>-4.0539105395904897</v>
+      </c>
+      <c r="Q120">
+        <v>-3.43591056493594</v>
+      </c>
+      <c r="R120">
+        <v>-3.49886769771524</v>
+      </c>
+      <c r="S120">
+        <v>3.49886769771524</v>
+      </c>
+      <c r="T120" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>141</v>
       </c>
@@ -5532,8 +7846,27 @@
       <c r="M121">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O121">
+        <v>-1.45</v>
+      </c>
+      <c r="P121">
+        <v>-1.4335325212052299</v>
+      </c>
+      <c r="Q121">
+        <v>-1.35587637758079</v>
+      </c>
+      <c r="R121">
+        <v>-1.30541179260381</v>
+      </c>
+      <c r="S121">
+        <v>1.30541179260381</v>
+      </c>
+      <c r="T121" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>142</v>
       </c>
@@ -5573,8 +7906,27 @@
       <c r="M122">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O122">
+        <v>-0.56499999999999995</v>
+      </c>
+      <c r="P122">
+        <v>-0.58213790077641803</v>
+      </c>
+      <c r="Q122">
+        <v>-0.50943845060667503</v>
+      </c>
+      <c r="R122">
+        <v>-0.52695630826032003</v>
+      </c>
+      <c r="S122">
+        <v>0.52695630826032003</v>
+      </c>
+      <c r="T122" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>143</v>
       </c>
@@ -5614,8 +7966,27 @@
       <c r="M123">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O123">
+        <v>-0.89500000000000002</v>
+      </c>
+      <c r="P123">
+        <v>-1.0153092371458901</v>
+      </c>
+      <c r="Q123">
+        <v>-0.89339686810253804</v>
+      </c>
+      <c r="R123">
+        <v>-0.76803918290818296</v>
+      </c>
+      <c r="S123">
+        <v>0.76803918290818296</v>
+      </c>
+      <c r="T123" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>144</v>
       </c>
@@ -5655,8 +8026,27 @@
       <c r="M124">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+      <c r="Q124">
+        <v>0</v>
+      </c>
+      <c r="R124">
+        <v>0</v>
+      </c>
+      <c r="S124">
+        <v>0</v>
+      </c>
+      <c r="T124" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>145</v>
       </c>
@@ -5696,8 +8086,27 @@
       <c r="M125">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O125">
+        <v>-0.24</v>
+      </c>
+      <c r="P125">
+        <v>-0.246832149161964</v>
+      </c>
+      <c r="Q125">
+        <v>-0.23262123078865801</v>
+      </c>
+      <c r="R125">
+        <v>-0.20849491360012301</v>
+      </c>
+      <c r="S125">
+        <v>0.20849491360012301</v>
+      </c>
+      <c r="T125" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>146</v>
       </c>
@@ -5737,8 +8146,27 @@
       <c r="M126">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+      <c r="Q126">
+        <v>0</v>
+      </c>
+      <c r="R126">
+        <v>0</v>
+      </c>
+      <c r="S126">
+        <v>0</v>
+      </c>
+      <c r="T126" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>147</v>
       </c>
@@ -5778,8 +8206,27 @@
       <c r="M127">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>0</v>
+      </c>
+      <c r="Q127">
+        <v>0</v>
+      </c>
+      <c r="R127">
+        <v>0</v>
+      </c>
+      <c r="S127">
+        <v>0</v>
+      </c>
+      <c r="T127" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>148</v>
       </c>
@@ -5819,8 +8266,27 @@
       <c r="M128">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O128">
+        <v>-0.63</v>
+      </c>
+      <c r="P128">
+        <v>-0.63452886059170699</v>
+      </c>
+      <c r="Q128">
+        <v>-0.63190849830310702</v>
+      </c>
+      <c r="R128">
+        <v>-0.561676065864122</v>
+      </c>
+      <c r="S128">
+        <v>0.561676065864122</v>
+      </c>
+      <c r="T128" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>149</v>
       </c>
@@ -5860,8 +8326,27 @@
       <c r="M129">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>0</v>
+      </c>
+      <c r="Q129">
+        <v>0</v>
+      </c>
+      <c r="R129">
+        <v>0</v>
+      </c>
+      <c r="S129">
+        <v>0</v>
+      </c>
+      <c r="T129" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>150</v>
       </c>
@@ -5901,8 +8386,27 @@
       <c r="M130">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>0</v>
+      </c>
+      <c r="Q130">
+        <v>0</v>
+      </c>
+      <c r="R130">
+        <v>0</v>
+      </c>
+      <c r="S130">
+        <v>0</v>
+      </c>
+      <c r="T130" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>151</v>
       </c>
@@ -5942,8 +8446,27 @@
       <c r="M131">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
+      </c>
+      <c r="Q131">
+        <v>0</v>
+      </c>
+      <c r="R131">
+        <v>0</v>
+      </c>
+      <c r="S131">
+        <v>0</v>
+      </c>
+      <c r="T131" t="b">
+        <f t="shared" ref="T131:T194" si="2">R131=-S131</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>152</v>
       </c>
@@ -5983,8 +8506,27 @@
       <c r="M132">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O132">
+        <v>-0.17</v>
+      </c>
+      <c r="P132">
+        <v>-0.16606577603897199</v>
+      </c>
+      <c r="Q132">
+        <v>-0.165777913628466</v>
+      </c>
+      <c r="R132">
+        <v>-0.148094988851455</v>
+      </c>
+      <c r="S132">
+        <v>0.148094988851455</v>
+      </c>
+      <c r="T132" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>153</v>
       </c>
@@ -6024,8 +8566,27 @@
       <c r="M133">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+      <c r="Q133">
+        <v>0</v>
+      </c>
+      <c r="R133">
+        <v>0</v>
+      </c>
+      <c r="S133">
+        <v>0</v>
+      </c>
+      <c r="T133" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>154</v>
       </c>
@@ -6065,8 +8626,27 @@
       <c r="M134">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O134">
+        <v>-0.7</v>
+      </c>
+      <c r="P134">
+        <v>-0.76605072460138701</v>
+      </c>
+      <c r="Q134">
+        <v>-0.66250436283131597</v>
+      </c>
+      <c r="R134">
+        <v>-0.653228075934286</v>
+      </c>
+      <c r="S134">
+        <v>0.653228075934286</v>
+      </c>
+      <c r="T134" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>155</v>
       </c>
@@ -6106,8 +8686,27 @@
       <c r="M135">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O135">
+        <v>-2</v>
+      </c>
+      <c r="P135">
+        <v>-2.24106674649622</v>
+      </c>
+      <c r="Q135">
+        <v>-1.8088563617662199</v>
+      </c>
+      <c r="R135">
+        <v>-1.7455091156126801</v>
+      </c>
+      <c r="S135">
+        <v>1.7455091156126801</v>
+      </c>
+      <c r="T135" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>156</v>
       </c>
@@ -6147,8 +8746,27 @@
       <c r="M136">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O136">
+        <v>-0.75</v>
+      </c>
+      <c r="P136">
+        <v>-0.80126148170713296</v>
+      </c>
+      <c r="Q136">
+        <v>-0.71992114057847201</v>
+      </c>
+      <c r="R136">
+        <v>-0.647277019367682</v>
+      </c>
+      <c r="S136">
+        <v>0.647277019367682</v>
+      </c>
+      <c r="T136" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>157</v>
       </c>
@@ -6188,8 +8806,27 @@
       <c r="M137">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O137">
+        <v>-1.2350000000000001</v>
+      </c>
+      <c r="P137">
+        <v>-1.26099595669967</v>
+      </c>
+      <c r="Q137">
+        <v>-1.1642782304261099</v>
+      </c>
+      <c r="R137">
+        <v>-1.1073464027773801</v>
+      </c>
+      <c r="S137">
+        <v>1.1073464027773801</v>
+      </c>
+      <c r="T137" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>158</v>
       </c>
@@ -6229,8 +8866,27 @@
       <c r="M138">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>0</v>
+      </c>
+      <c r="R138">
+        <v>0</v>
+      </c>
+      <c r="S138">
+        <v>0</v>
+      </c>
+      <c r="T138" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>159</v>
       </c>
@@ -6270,8 +8926,27 @@
       <c r="M139">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O139">
+        <v>-0.33</v>
+      </c>
+      <c r="P139">
+        <v>-0.372705608576612</v>
+      </c>
+      <c r="Q139">
+        <v>-0.29036636057967002</v>
+      </c>
+      <c r="R139">
+        <v>-0.28882202809709701</v>
+      </c>
+      <c r="S139">
+        <v>0.28882202809709701</v>
+      </c>
+      <c r="T139" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>160</v>
       </c>
@@ -6311,8 +8986,27 @@
       <c r="M140">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="Q140">
+        <v>0</v>
+      </c>
+      <c r="R140">
+        <v>0</v>
+      </c>
+      <c r="S140">
+        <v>0</v>
+      </c>
+      <c r="T140" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>161</v>
       </c>
@@ -6352,8 +9046,27 @@
       <c r="M141">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O141">
+        <v>-0.35</v>
+      </c>
+      <c r="P141">
+        <v>-0.381507169327921</v>
+      </c>
+      <c r="Q141">
+        <v>-0.32780874188418802</v>
+      </c>
+      <c r="R141">
+        <v>-0.30254445995810503</v>
+      </c>
+      <c r="S141">
+        <v>0.30254445995810503</v>
+      </c>
+      <c r="T141" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>162</v>
       </c>
@@ -6393,8 +9106,27 @@
       <c r="M142">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O142">
+        <v>-0.85</v>
+      </c>
+      <c r="P142">
+        <v>-0.80855049714160498</v>
+      </c>
+      <c r="Q142">
+        <v>-0.75656065325396704</v>
+      </c>
+      <c r="R142">
+        <v>-0.78617915640737801</v>
+      </c>
+      <c r="S142">
+        <v>0.78617915640737801</v>
+      </c>
+      <c r="T142" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>163</v>
       </c>
@@ -6434,8 +9166,27 @@
       <c r="M143">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O143">
+        <v>0</v>
+      </c>
+      <c r="P143">
+        <v>0</v>
+      </c>
+      <c r="Q143">
+        <v>0</v>
+      </c>
+      <c r="R143">
+        <v>0</v>
+      </c>
+      <c r="S143">
+        <v>0</v>
+      </c>
+      <c r="T143" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>164</v>
       </c>
@@ -6475,8 +9226,27 @@
       <c r="M144">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144">
+        <v>0</v>
+      </c>
+      <c r="Q144">
+        <v>0</v>
+      </c>
+      <c r="R144">
+        <v>0</v>
+      </c>
+      <c r="S144">
+        <v>0</v>
+      </c>
+      <c r="T144" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>165</v>
       </c>
@@ -6516,8 +9286,27 @@
       <c r="M145">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O145">
+        <v>0</v>
+      </c>
+      <c r="P145">
+        <v>0</v>
+      </c>
+      <c r="Q145">
+        <v>0</v>
+      </c>
+      <c r="R145">
+        <v>0</v>
+      </c>
+      <c r="S145">
+        <v>0</v>
+      </c>
+      <c r="T145" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>166</v>
       </c>
@@ -6557,8 +9346,27 @@
       <c r="M146">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O146">
+        <v>0</v>
+      </c>
+      <c r="P146">
+        <v>0</v>
+      </c>
+      <c r="Q146">
+        <v>0</v>
+      </c>
+      <c r="R146">
+        <v>0</v>
+      </c>
+      <c r="S146">
+        <v>0</v>
+      </c>
+      <c r="T146" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>167</v>
       </c>
@@ -6598,8 +9406,27 @@
       <c r="M147">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O147">
+        <v>-2.9989999999999899</v>
+      </c>
+      <c r="P147">
+        <v>-3.08342844867372</v>
+      </c>
+      <c r="Q147">
+        <v>-2.7032796675905302</v>
+      </c>
+      <c r="R147">
+        <v>-2.6618960640285301</v>
+      </c>
+      <c r="S147">
+        <v>2.6618960640285301</v>
+      </c>
+      <c r="T147" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>168</v>
       </c>
@@ -6639,8 +9466,27 @@
       <c r="M148">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O148">
+        <v>0</v>
+      </c>
+      <c r="P148">
+        <v>0</v>
+      </c>
+      <c r="Q148">
+        <v>0</v>
+      </c>
+      <c r="R148">
+        <v>0</v>
+      </c>
+      <c r="S148">
+        <v>0</v>
+      </c>
+      <c r="T148" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>169</v>
       </c>
@@ -6680,8 +9526,27 @@
       <c r="M149">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O149">
+        <v>0</v>
+      </c>
+      <c r="P149">
+        <v>0</v>
+      </c>
+      <c r="Q149">
+        <v>0</v>
+      </c>
+      <c r="R149">
+        <v>0</v>
+      </c>
+      <c r="S149">
+        <v>0</v>
+      </c>
+      <c r="T149" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>170</v>
       </c>
@@ -6721,8 +9586,27 @@
       <c r="M150">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O150">
+        <v>-4.8179999999999996</v>
+      </c>
+      <c r="P150">
+        <v>-4.9069731944292503</v>
+      </c>
+      <c r="Q150">
+        <v>-4.4314804899079503</v>
+      </c>
+      <c r="R150">
+        <v>-4.1913990102589196</v>
+      </c>
+      <c r="S150">
+        <v>4.1913990102589196</v>
+      </c>
+      <c r="T150" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>171</v>
       </c>
@@ -6762,8 +9646,27 @@
       <c r="M151">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O151">
+        <v>-7.6360000000000001</v>
+      </c>
+      <c r="P151">
+        <v>-7.6344097591036002</v>
+      </c>
+      <c r="Q151">
+        <v>-6.9722142527020701</v>
+      </c>
+      <c r="R151">
+        <v>-6.8043445724588896</v>
+      </c>
+      <c r="S151">
+        <v>6.8043445724588896</v>
+      </c>
+      <c r="T151" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>172</v>
       </c>
@@ -6803,8 +9706,27 @@
       <c r="M152">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O152">
+        <v>-0.26500000000000001</v>
+      </c>
+      <c r="P152">
+        <v>-0.28305684737227499</v>
+      </c>
+      <c r="Q152">
+        <v>-0.25604813061825599</v>
+      </c>
+      <c r="R152">
+        <v>-0.234246278000041</v>
+      </c>
+      <c r="S152">
+        <v>0.234246278000041</v>
+      </c>
+      <c r="T152" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>173</v>
       </c>
@@ -6844,8 +9766,27 @@
       <c r="M153">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O153">
+        <v>-1.635</v>
+      </c>
+      <c r="P153">
+        <v>-1.7803406804408299</v>
+      </c>
+      <c r="Q153">
+        <v>-1.4483365677350599</v>
+      </c>
+      <c r="R153">
+        <v>-1.40069751151727</v>
+      </c>
+      <c r="S153">
+        <v>1.40069751151727</v>
+      </c>
+      <c r="T153" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>174</v>
       </c>
@@ -6885,8 +9826,27 @@
       <c r="M154">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="P154">
+        <v>0</v>
+      </c>
+      <c r="Q154">
+        <v>0</v>
+      </c>
+      <c r="R154">
+        <v>0</v>
+      </c>
+      <c r="S154">
+        <v>0</v>
+      </c>
+      <c r="T154" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>175</v>
       </c>
@@ -6926,8 +9886,27 @@
       <c r="M155">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O155">
+        <v>-1.76</v>
+      </c>
+      <c r="P155">
+        <v>-1.75354229028796</v>
+      </c>
+      <c r="Q155">
+        <v>-1.66393659153582</v>
+      </c>
+      <c r="R155">
+        <v>-1.69239222231794</v>
+      </c>
+      <c r="S155">
+        <v>1.69239222231794</v>
+      </c>
+      <c r="T155" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>176</v>
       </c>
@@ -6967,8 +9946,27 @@
       <c r="M156">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O156">
+        <v>-0.05</v>
+      </c>
+      <c r="P156">
+        <v>-5.4775953774752799E-2</v>
+      </c>
+      <c r="Q156">
+        <v>-5.1394825799302699E-2</v>
+      </c>
+      <c r="R156">
+        <v>-4.0284520456608297E-2</v>
+      </c>
+      <c r="S156">
+        <v>4.0284520456608297E-2</v>
+      </c>
+      <c r="T156" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>177</v>
       </c>
@@ -7008,8 +10006,27 @@
       <c r="M157">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O157">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="P157">
+        <v>-0.28513469797941698</v>
+      </c>
+      <c r="Q157">
+        <v>-0.26891146257141602</v>
+      </c>
+      <c r="R157">
+        <v>-0.24679214191225099</v>
+      </c>
+      <c r="S157">
+        <v>0.24679214191225099</v>
+      </c>
+      <c r="T157" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>178</v>
       </c>
@@ -7049,8 +10066,27 @@
       <c r="M158">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O158">
+        <v>-4.274</v>
+      </c>
+      <c r="P158">
+        <v>-4.5411251120358003</v>
+      </c>
+      <c r="Q158">
+        <v>-4.0847896142134097</v>
+      </c>
+      <c r="R158">
+        <v>-4.0937010003107099</v>
+      </c>
+      <c r="S158">
+        <v>4.0937010003107099</v>
+      </c>
+      <c r="T158" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>179</v>
       </c>
@@ -7090,8 +10126,27 @@
       <c r="M159">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O159">
+        <v>-0.74</v>
+      </c>
+      <c r="P159">
+        <v>-0.72276549198337703</v>
+      </c>
+      <c r="Q159">
+        <v>-0.66193417029119594</v>
+      </c>
+      <c r="R159">
+        <v>-0.72538366569808499</v>
+      </c>
+      <c r="S159">
+        <v>0.72538366569808499</v>
+      </c>
+      <c r="T159" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>180</v>
       </c>
@@ -7131,8 +10186,27 @@
       <c r="M160">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O160">
+        <v>-0.69499999999999995</v>
+      </c>
+      <c r="P160">
+        <v>-0.70617598779128699</v>
+      </c>
+      <c r="Q160">
+        <v>-0.66094368807310899</v>
+      </c>
+      <c r="R160">
+        <v>-0.64356278324939098</v>
+      </c>
+      <c r="S160">
+        <v>0.64356278324939098</v>
+      </c>
+      <c r="T160" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>181</v>
       </c>
@@ -7172,8 +10246,27 @@
       <c r="M161">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O161">
+        <v>-0.73399999999999999</v>
+      </c>
+      <c r="P161">
+        <v>-0.77560147441397198</v>
+      </c>
+      <c r="Q161">
+        <v>-0.68253536179641305</v>
+      </c>
+      <c r="R161">
+        <v>-0.66184646646442302</v>
+      </c>
+      <c r="S161">
+        <v>0.66184646646442302</v>
+      </c>
+      <c r="T161" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>182</v>
       </c>
@@ -7213,8 +10306,27 @@
       <c r="M162">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O162">
+        <v>-2.407</v>
+      </c>
+      <c r="P162">
+        <v>-2.7207167450183798</v>
+      </c>
+      <c r="Q162">
+        <v>-2.19443517505184</v>
+      </c>
+      <c r="R162">
+        <v>-2.09967242456367</v>
+      </c>
+      <c r="S162">
+        <v>2.09967242456367</v>
+      </c>
+      <c r="T162" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>183</v>
       </c>
@@ -7254,8 +10366,27 @@
       <c r="M163">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O163">
+        <v>-0.4</v>
+      </c>
+      <c r="P163">
+        <v>-0.41577023390576001</v>
+      </c>
+      <c r="Q163">
+        <v>-0.393418550923889</v>
+      </c>
+      <c r="R163">
+        <v>-0.34018912093925502</v>
+      </c>
+      <c r="S163">
+        <v>0.34018912093925502</v>
+      </c>
+      <c r="T163" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>184</v>
       </c>
@@ -7295,8 +10426,27 @@
       <c r="M164">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O164">
+        <v>-1.3680000000000001</v>
+      </c>
+      <c r="P164">
+        <v>-1.3829999590995301</v>
+      </c>
+      <c r="Q164">
+        <v>-1.3137881865008401</v>
+      </c>
+      <c r="R164">
+        <v>-1.27827860307133</v>
+      </c>
+      <c r="S164">
+        <v>1.27827860307133</v>
+      </c>
+      <c r="T164" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>185</v>
       </c>
@@ -7336,8 +10486,27 @@
       <c r="M165">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O165">
+        <v>0</v>
+      </c>
+      <c r="P165">
+        <v>0</v>
+      </c>
+      <c r="Q165">
+        <v>0</v>
+      </c>
+      <c r="R165">
+        <v>0</v>
+      </c>
+      <c r="S165">
+        <v>0</v>
+      </c>
+      <c r="T165" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>186</v>
       </c>
@@ -7377,8 +10546,27 @@
       <c r="M166">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O166">
+        <v>-0.59799999999999998</v>
+      </c>
+      <c r="P166">
+        <v>-0.67310368547822097</v>
+      </c>
+      <c r="Q166">
+        <v>-0.60718402676927297</v>
+      </c>
+      <c r="R166">
+        <v>-0.58109847193046404</v>
+      </c>
+      <c r="S166">
+        <v>0.58109847193046404</v>
+      </c>
+      <c r="T166" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>187</v>
       </c>
@@ -7418,8 +10606,27 @@
       <c r="M167">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O167">
+        <v>-0.59799999999999998</v>
+      </c>
+      <c r="P167">
+        <v>-0.63313257163124703</v>
+      </c>
+      <c r="Q167">
+        <v>-0.58372951252233196</v>
+      </c>
+      <c r="R167">
+        <v>-0.56235158074943503</v>
+      </c>
+      <c r="S167">
+        <v>0.56235158074943503</v>
+      </c>
+      <c r="T167" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>188</v>
       </c>
@@ -7459,8 +10666,27 @@
       <c r="M168">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O168">
+        <v>-1.8259999999999901</v>
+      </c>
+      <c r="P168">
+        <v>-2.0307527644131298</v>
+      </c>
+      <c r="Q168">
+        <v>-1.59410335375446</v>
+      </c>
+      <c r="R168">
+        <v>-1.56114638290317</v>
+      </c>
+      <c r="S168">
+        <v>1.56114638290317</v>
+      </c>
+      <c r="T168" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>189</v>
       </c>
@@ -7500,8 +10726,27 @@
       <c r="M169">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O169">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="P169">
+        <v>-6.7181251015027393E-2</v>
+      </c>
+      <c r="Q169">
+        <v>-6.5382446996548493E-2</v>
+      </c>
+      <c r="R169">
+        <v>-5.8592172678418902E-2</v>
+      </c>
+      <c r="S169">
+        <v>5.8592172678418902E-2</v>
+      </c>
+      <c r="T169" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>190</v>
       </c>
@@ -7541,8 +10786,27 @@
       <c r="M170">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O170">
+        <v>0</v>
+      </c>
+      <c r="P170">
+        <v>0</v>
+      </c>
+      <c r="Q170">
+        <v>0</v>
+      </c>
+      <c r="R170">
+        <v>0</v>
+      </c>
+      <c r="S170">
+        <v>0</v>
+      </c>
+      <c r="T170" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>191</v>
       </c>
@@ -7582,8 +10846,27 @@
       <c r="M171">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O171">
+        <v>-4.8899999999999997</v>
+      </c>
+      <c r="P171">
+        <v>-5.1519970917695499</v>
+      </c>
+      <c r="Q171">
+        <v>-4.5664253742330603</v>
+      </c>
+      <c r="R171">
+        <v>-4.2677984823344</v>
+      </c>
+      <c r="S171">
+        <v>4.2677984823344</v>
+      </c>
+      <c r="T171" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>192</v>
       </c>
@@ -7623,8 +10906,27 @@
       <c r="M172">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O172">
+        <v>-8</v>
+      </c>
+      <c r="P172">
+        <v>-8.4934983158948807</v>
+      </c>
+      <c r="Q172">
+        <v>-7.0380547085459302</v>
+      </c>
+      <c r="R172">
+        <v>-7.0305354714970303</v>
+      </c>
+      <c r="S172">
+        <v>7.0305354714970303</v>
+      </c>
+      <c r="T172" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>193</v>
       </c>
@@ -7664,8 +10966,27 @@
       <c r="M173">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O173">
+        <v>0</v>
+      </c>
+      <c r="P173">
+        <v>0</v>
+      </c>
+      <c r="Q173">
+        <v>0</v>
+      </c>
+      <c r="R173">
+        <v>0</v>
+      </c>
+      <c r="S173">
+        <v>0</v>
+      </c>
+      <c r="T173" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>194</v>
       </c>
@@ -7705,8 +11026,27 @@
       <c r="M174">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O174">
+        <v>0</v>
+      </c>
+      <c r="P174">
+        <v>0</v>
+      </c>
+      <c r="Q174">
+        <v>0</v>
+      </c>
+      <c r="R174">
+        <v>0</v>
+      </c>
+      <c r="S174">
+        <v>0</v>
+      </c>
+      <c r="T174" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>195</v>
       </c>
@@ -7746,8 +11086,27 @@
       <c r="M175">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O175">
+        <v>0</v>
+      </c>
+      <c r="P175">
+        <v>0</v>
+      </c>
+      <c r="Q175">
+        <v>0</v>
+      </c>
+      <c r="R175">
+        <v>0</v>
+      </c>
+      <c r="S175">
+        <v>0</v>
+      </c>
+      <c r="T175" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>196</v>
       </c>
@@ -7787,8 +11146,27 @@
       <c r="M176">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O176">
+        <v>-0.1</v>
+      </c>
+      <c r="P176">
+        <v>-0.11214962015864301</v>
+      </c>
+      <c r="Q176">
+        <v>-9.9365147646907695E-2</v>
+      </c>
+      <c r="R176">
+        <v>-9.0625563005485299E-2</v>
+      </c>
+      <c r="S176">
+        <v>9.0625563005485299E-2</v>
+      </c>
+      <c r="T176" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>197</v>
       </c>
@@ -7828,8 +11206,27 @@
       <c r="M177">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O177">
+        <v>-0.43</v>
+      </c>
+      <c r="P177">
+        <v>-0.437588691195892</v>
+      </c>
+      <c r="Q177">
+        <v>-0.39097785141549601</v>
+      </c>
+      <c r="R177">
+        <v>-0.36369984576494602</v>
+      </c>
+      <c r="S177">
+        <v>0.36369984576494602</v>
+      </c>
+      <c r="T177" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>198</v>
       </c>
@@ -7869,8 +11266,27 @@
       <c r="M178">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O178">
+        <v>-0.64</v>
+      </c>
+      <c r="P178">
+        <v>-0.68389217641984901</v>
+      </c>
+      <c r="Q178">
+        <v>-0.57073962283353497</v>
+      </c>
+      <c r="R178">
+        <v>-0.56201518750667501</v>
+      </c>
+      <c r="S178">
+        <v>0.56201518750667501</v>
+      </c>
+      <c r="T178" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>199</v>
       </c>
@@ -7910,8 +11326,27 @@
       <c r="M179">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O179">
+        <v>-0.35</v>
+      </c>
+      <c r="P179">
+        <v>-0.380295486877542</v>
+      </c>
+      <c r="Q179">
+        <v>-0.30954719400636299</v>
+      </c>
+      <c r="R179">
+        <v>-0.29304123551581901</v>
+      </c>
+      <c r="S179">
+        <v>0.29304123551581901</v>
+      </c>
+      <c r="T179" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>200</v>
       </c>
@@ -7951,8 +11386,27 @@
       <c r="M180">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O180">
+        <v>-0.27</v>
+      </c>
+      <c r="P180">
+        <v>-0.287329763759757</v>
+      </c>
+      <c r="Q180">
+        <v>-0.25278655762368202</v>
+      </c>
+      <c r="R180">
+        <v>-0.26366740774973701</v>
+      </c>
+      <c r="S180">
+        <v>0.26366740774973701</v>
+      </c>
+      <c r="T180" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>201</v>
       </c>
@@ -7992,8 +11446,27 @@
       <c r="M181">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O181">
+        <v>-0.41</v>
+      </c>
+      <c r="P181">
+        <v>-0.451610198175462</v>
+      </c>
+      <c r="Q181">
+        <v>-0.38547016480866098</v>
+      </c>
+      <c r="R181">
+        <v>-0.34112254998588598</v>
+      </c>
+      <c r="S181">
+        <v>0.34112254998588598</v>
+      </c>
+      <c r="T181" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>202</v>
       </c>
@@ -8033,8 +11506,27 @@
       <c r="M182">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O182">
+        <v>-0.38</v>
+      </c>
+      <c r="P182">
+        <v>-0.40739888466574797</v>
+      </c>
+      <c r="Q182">
+        <v>-0.33090982337536001</v>
+      </c>
+      <c r="R182">
+        <v>-0.33201736270719401</v>
+      </c>
+      <c r="S182">
+        <v>0.33201736270719401</v>
+      </c>
+      <c r="T182" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>203</v>
       </c>
@@ -8074,8 +11566,27 @@
       <c r="M183">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O183">
+        <v>-0.42</v>
+      </c>
+      <c r="P183">
+        <v>-0.47642035118089499</v>
+      </c>
+      <c r="Q183">
+        <v>-0.39187834476846001</v>
+      </c>
+      <c r="R183">
+        <v>-0.357950316023874</v>
+      </c>
+      <c r="S183">
+        <v>0.357950316023874</v>
+      </c>
+      <c r="T183" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>204</v>
       </c>
@@ -8115,8 +11626,27 @@
       <c r="M184">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O184">
+        <v>-0.72</v>
+      </c>
+      <c r="P184">
+        <v>-0.76717960726690904</v>
+      </c>
+      <c r="Q184">
+        <v>-0.71390499480576097</v>
+      </c>
+      <c r="R184">
+        <v>-0.66525509660751903</v>
+      </c>
+      <c r="S184">
+        <v>0.66525509660751903</v>
+      </c>
+      <c r="T184" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>205</v>
       </c>
@@ -8156,8 +11686,27 @@
       <c r="M185">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O185">
+        <v>0</v>
+      </c>
+      <c r="P185">
+        <v>0</v>
+      </c>
+      <c r="Q185">
+        <v>0</v>
+      </c>
+      <c r="R185">
+        <v>0</v>
+      </c>
+      <c r="S185">
+        <v>0</v>
+      </c>
+      <c r="T185" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>206</v>
       </c>
@@ -8197,8 +11746,27 @@
       <c r="M186">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O186">
+        <v>-0.12</v>
+      </c>
+      <c r="P186">
+        <v>-0.13012291445291099</v>
+      </c>
+      <c r="Q186">
+        <v>-0.117970090279142</v>
+      </c>
+      <c r="R186">
+        <v>-0.11281542708869</v>
+      </c>
+      <c r="S186">
+        <v>0.11281542708869</v>
+      </c>
+      <c r="T186" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>207</v>
       </c>
@@ -8238,8 +11806,27 @@
       <c r="M187">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O187">
+        <v>0.21</v>
+      </c>
+      <c r="P187">
+        <v>0.19200862914429001</v>
+      </c>
+      <c r="Q187">
+        <v>0.19944174273792001</v>
+      </c>
+      <c r="R187">
+        <v>0.17762538353968599</v>
+      </c>
+      <c r="S187">
+        <v>-0.17762538353968599</v>
+      </c>
+      <c r="T187" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>208</v>
       </c>
@@ -8279,8 +11866,27 @@
       <c r="M188">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O188">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="P188">
+        <v>-6.4131324875488602E-2</v>
+      </c>
+      <c r="Q188">
+        <v>-7.1897258316637902E-2</v>
+      </c>
+      <c r="R188">
+        <v>-5.7341181226906103E-2</v>
+      </c>
+      <c r="S188">
+        <v>5.7341181226906103E-2</v>
+      </c>
+      <c r="T188" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>209</v>
       </c>
@@ -8320,8 +11926,27 @@
       <c r="M189">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O189">
+        <v>-0.38</v>
+      </c>
+      <c r="P189">
+        <v>-0.40276591830205799</v>
+      </c>
+      <c r="Q189">
+        <v>-0.35834302291338399</v>
+      </c>
+      <c r="R189">
+        <v>-0.333278823339479</v>
+      </c>
+      <c r="S189">
+        <v>0.333278823339479</v>
+      </c>
+      <c r="T189" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>210</v>
       </c>
@@ -8361,8 +11986,27 @@
       <c r="M190">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O190">
+        <v>0</v>
+      </c>
+      <c r="P190">
+        <v>0</v>
+      </c>
+      <c r="Q190">
+        <v>0</v>
+      </c>
+      <c r="R190">
+        <v>0</v>
+      </c>
+      <c r="S190">
+        <v>0</v>
+      </c>
+      <c r="T190" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>211</v>
       </c>
@@ -8402,8 +12046,27 @@
       <c r="M191">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O191">
+        <v>-0.96</v>
+      </c>
+      <c r="P191">
+        <v>-1.06737514905006</v>
+      </c>
+      <c r="Q191">
+        <v>-0.89368821775284202</v>
+      </c>
+      <c r="R191">
+        <v>-0.92016581018843302</v>
+      </c>
+      <c r="S191">
+        <v>0.92016581018843302</v>
+      </c>
+      <c r="T191" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>212</v>
       </c>
@@ -8443,8 +12106,27 @@
       <c r="M192">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O192">
+        <v>0</v>
+      </c>
+      <c r="P192">
+        <v>0</v>
+      </c>
+      <c r="Q192">
+        <v>0</v>
+      </c>
+      <c r="R192">
+        <v>0</v>
+      </c>
+      <c r="S192">
+        <v>0</v>
+      </c>
+      <c r="T192" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>213</v>
       </c>
@@ -8484,8 +12166,27 @@
       <c r="M193">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O193">
+        <v>0</v>
+      </c>
+      <c r="P193">
+        <v>0</v>
+      </c>
+      <c r="Q193">
+        <v>0</v>
+      </c>
+      <c r="R193">
+        <v>0</v>
+      </c>
+      <c r="S193">
+        <v>0</v>
+      </c>
+      <c r="T193" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>214</v>
       </c>
@@ -8525,8 +12226,27 @@
       <c r="M194">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O194">
+        <v>-0.22</v>
+      </c>
+      <c r="P194">
+        <v>-0.208302826134801</v>
+      </c>
+      <c r="Q194">
+        <v>-0.195804194367875</v>
+      </c>
+      <c r="R194">
+        <v>-0.18439617522421101</v>
+      </c>
+      <c r="S194">
+        <v>0.18439617522421101</v>
+      </c>
+      <c r="T194" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>215</v>
       </c>
@@ -8566,8 +12286,27 @@
       <c r="M195">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O195">
+        <v>-0.47</v>
+      </c>
+      <c r="P195">
+        <v>-0.48641487193456001</v>
+      </c>
+      <c r="Q195">
+        <v>-0.44774514830335999</v>
+      </c>
+      <c r="R195">
+        <v>-0.41622394705305299</v>
+      </c>
+      <c r="S195">
+        <v>0.41622394705305299</v>
+      </c>
+      <c r="T195" t="b">
+        <f t="shared" ref="T195:T258" si="3">R195=-S195</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>216</v>
       </c>
@@ -8607,8 +12346,27 @@
       <c r="M196">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O196">
+        <v>-1.76</v>
+      </c>
+      <c r="P196">
+        <v>-1.79181944003673</v>
+      </c>
+      <c r="Q196">
+        <v>-1.6125553486717299</v>
+      </c>
+      <c r="R196">
+        <v>-1.47967821300963</v>
+      </c>
+      <c r="S196">
+        <v>1.47967821300963</v>
+      </c>
+      <c r="T196" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>217</v>
       </c>
@@ -8648,8 +12406,27 @@
       <c r="M197">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O197">
+        <v>-1</v>
+      </c>
+      <c r="P197">
+        <v>-0.99130278506298297</v>
+      </c>
+      <c r="Q197">
+        <v>-0.95381114062356898</v>
+      </c>
+      <c r="R197">
+        <v>-0.88637658629932403</v>
+      </c>
+      <c r="S197">
+        <v>0.88637658629932403</v>
+      </c>
+      <c r="T197" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>218</v>
       </c>
@@ -8689,8 +12466,27 @@
       <c r="M198">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O198">
+        <v>-1.31</v>
+      </c>
+      <c r="P198">
+        <v>-1.25381613244731</v>
+      </c>
+      <c r="Q198">
+        <v>-1.1259640310645</v>
+      </c>
+      <c r="R198">
+        <v>-1.17721046317472</v>
+      </c>
+      <c r="S198">
+        <v>1.17721046317472</v>
+      </c>
+      <c r="T198" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>219</v>
       </c>
@@ -8730,8 +12526,27 @@
       <c r="M199">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O199">
+        <v>0</v>
+      </c>
+      <c r="P199">
+        <v>0</v>
+      </c>
+      <c r="Q199">
+        <v>0</v>
+      </c>
+      <c r="R199">
+        <v>0</v>
+      </c>
+      <c r="S199">
+        <v>0</v>
+      </c>
+      <c r="T199" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>220</v>
       </c>
@@ -8771,8 +12586,27 @@
       <c r="M200">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O200">
+        <v>-2.85</v>
+      </c>
+      <c r="P200">
+        <v>-2.9654555190768499</v>
+      </c>
+      <c r="Q200">
+        <v>-2.5320058002896402</v>
+      </c>
+      <c r="R200">
+        <v>-2.3568160516290702</v>
+      </c>
+      <c r="S200">
+        <v>2.3568160516290702</v>
+      </c>
+      <c r="T200" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>221</v>
       </c>
@@ -8812,8 +12646,27 @@
       <c r="M201">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O201">
+        <v>-1.71</v>
+      </c>
+      <c r="P201">
+        <v>-1.76838026338156</v>
+      </c>
+      <c r="Q201">
+        <v>-1.7045167445768401</v>
+      </c>
+      <c r="R201">
+        <v>-1.5465853618871199</v>
+      </c>
+      <c r="S201">
+        <v>1.5465853618871199</v>
+      </c>
+      <c r="T201" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>222</v>
       </c>
@@ -8853,8 +12706,27 @@
       <c r="M202">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O202">
+        <v>-3.28</v>
+      </c>
+      <c r="P202">
+        <v>-3.3103811100156499</v>
+      </c>
+      <c r="Q202">
+        <v>-2.9137781704131802</v>
+      </c>
+      <c r="R202">
+        <v>-2.68017934190109</v>
+      </c>
+      <c r="S202">
+        <v>2.68017934190109</v>
+      </c>
+      <c r="T202" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>223</v>
       </c>
@@ -8894,8 +12766,27 @@
       <c r="M203">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O203">
+        <v>-4.28</v>
+      </c>
+      <c r="P203">
+        <v>-4.1098656956797397</v>
+      </c>
+      <c r="Q203">
+        <v>-4.3148237325680601</v>
+      </c>
+      <c r="R203">
+        <v>-3.75441293330082</v>
+      </c>
+      <c r="S203">
+        <v>3.75441293330082</v>
+      </c>
+      <c r="T203" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>224</v>
       </c>
@@ -8935,8 +12826,27 @@
       <c r="M204">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O204">
+        <v>-1.73</v>
+      </c>
+      <c r="P204">
+        <v>-1.6371133273212399</v>
+      </c>
+      <c r="Q204">
+        <v>-1.56604602277886</v>
+      </c>
+      <c r="R204">
+        <v>-1.48048477664504</v>
+      </c>
+      <c r="S204">
+        <v>1.48048477664504</v>
+      </c>
+      <c r="T204" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>225</v>
       </c>
@@ -8976,8 +12886,27 @@
       <c r="M205">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O205">
+        <v>-4.0999999999999996</v>
+      </c>
+      <c r="P205">
+        <v>-3.9557067424235202</v>
+      </c>
+      <c r="Q205">
+        <v>-3.5458351241208601</v>
+      </c>
+      <c r="R205">
+        <v>-3.3500615198049299</v>
+      </c>
+      <c r="S205">
+        <v>3.3500615198049299</v>
+      </c>
+      <c r="T205" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>226</v>
       </c>
@@ -9017,8 +12946,27 @@
       <c r="M206">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O206">
+        <v>0</v>
+      </c>
+      <c r="P206">
+        <v>0</v>
+      </c>
+      <c r="Q206">
+        <v>0</v>
+      </c>
+      <c r="R206">
+        <v>0</v>
+      </c>
+      <c r="S206">
+        <v>0</v>
+      </c>
+      <c r="T206" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>227</v>
       </c>
@@ -9058,8 +13006,27 @@
       <c r="M207">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O207">
+        <v>-5.38</v>
+      </c>
+      <c r="P207">
+        <v>-5.5756836509867904</v>
+      </c>
+      <c r="Q207">
+        <v>-4.9059791246448299</v>
+      </c>
+      <c r="R207">
+        <v>-4.9362206607628503</v>
+      </c>
+      <c r="S207">
+        <v>4.9362206607628503</v>
+      </c>
+      <c r="T207" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>228</v>
       </c>
@@ -9099,8 +13066,27 @@
       <c r="M208">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O208">
+        <v>-2.23</v>
+      </c>
+      <c r="P208">
+        <v>-2.2635837265806802</v>
+      </c>
+      <c r="Q208">
+        <v>-2.3927139133354798</v>
+      </c>
+      <c r="R208">
+        <v>-2.1009750503370901</v>
+      </c>
+      <c r="S208">
+        <v>2.1009750503370901</v>
+      </c>
+      <c r="T208" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>229</v>
       </c>
@@ -9140,8 +13126,27 @@
       <c r="M209">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O209">
+        <v>-0.96</v>
+      </c>
+      <c r="P209">
+        <v>-1.0283351081729499</v>
+      </c>
+      <c r="Q209">
+        <v>-0.90717587709097902</v>
+      </c>
+      <c r="R209">
+        <v>-0.80541355197138298</v>
+      </c>
+      <c r="S209">
+        <v>0.80541355197138298</v>
+      </c>
+      <c r="T209" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>230</v>
       </c>
@@ -9181,8 +13186,27 @@
       <c r="M210">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O210">
+        <v>0</v>
+      </c>
+      <c r="P210">
+        <v>0</v>
+      </c>
+      <c r="Q210">
+        <v>0</v>
+      </c>
+      <c r="R210">
+        <v>0</v>
+      </c>
+      <c r="S210">
+        <v>0</v>
+      </c>
+      <c r="T210" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>231</v>
       </c>
@@ -9222,8 +13246,27 @@
       <c r="M211">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O211">
+        <v>-1.59</v>
+      </c>
+      <c r="P211">
+        <v>-1.6940707723847599</v>
+      </c>
+      <c r="Q211">
+        <v>-1.48701232141049</v>
+      </c>
+      <c r="R211">
+        <v>-1.4132723994629799</v>
+      </c>
+      <c r="S211">
+        <v>1.4132723994629799</v>
+      </c>
+      <c r="T211" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>232</v>
       </c>
@@ -9263,8 +13306,27 @@
       <c r="M212">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O212">
+        <v>-4.4800000000000004</v>
+      </c>
+      <c r="P212">
+        <v>-4.70483529585412</v>
+      </c>
+      <c r="Q212">
+        <v>-4.12800949267295</v>
+      </c>
+      <c r="R212">
+        <v>-3.8641845318234598</v>
+      </c>
+      <c r="S212">
+        <v>3.8641845318234598</v>
+      </c>
+      <c r="T212" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>233</v>
       </c>
@@ -9304,8 +13366,27 @@
       <c r="M213">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O213">
+        <v>-4.04</v>
+      </c>
+      <c r="P213">
+        <v>-4.19071393979028</v>
+      </c>
+      <c r="Q213">
+        <v>-3.6259352616395901</v>
+      </c>
+      <c r="R213">
+        <v>-4.05420176764967</v>
+      </c>
+      <c r="S213">
+        <v>4.05420176764967</v>
+      </c>
+      <c r="T213" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>234</v>
       </c>
@@ -9345,8 +13426,27 @@
       <c r="M214">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O214">
+        <v>-5.72</v>
+      </c>
+      <c r="P214">
+        <v>-5.77095948221179</v>
+      </c>
+      <c r="Q214">
+        <v>-5.1139051482257196</v>
+      </c>
+      <c r="R214">
+        <v>-5.3249535312546801</v>
+      </c>
+      <c r="S214">
+        <v>5.3249535312546801</v>
+      </c>
+      <c r="T214" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>235</v>
       </c>
@@ -9386,8 +13486,27 @@
       <c r="M215">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O215">
+        <v>-2.69</v>
+      </c>
+      <c r="P215">
+        <v>-2.7010731663664602</v>
+      </c>
+      <c r="Q215">
+        <v>-2.4254288010534601</v>
+      </c>
+      <c r="R215">
+        <v>-2.5329432991225298</v>
+      </c>
+      <c r="S215">
+        <v>2.5329432991225298</v>
+      </c>
+      <c r="T215" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>236</v>
       </c>
@@ -9427,8 +13546,27 @@
       <c r="M216">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O216">
+        <v>0</v>
+      </c>
+      <c r="P216">
+        <v>0</v>
+      </c>
+      <c r="Q216">
+        <v>0</v>
+      </c>
+      <c r="R216">
+        <v>0</v>
+      </c>
+      <c r="S216">
+        <v>0</v>
+      </c>
+      <c r="T216" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>237</v>
       </c>
@@ -9468,8 +13606,27 @@
       <c r="M217">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O217">
+        <v>0</v>
+      </c>
+      <c r="P217">
+        <v>0</v>
+      </c>
+      <c r="Q217">
+        <v>0</v>
+      </c>
+      <c r="R217">
+        <v>0</v>
+      </c>
+      <c r="S217">
+        <v>0</v>
+      </c>
+      <c r="T217" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>238</v>
       </c>
@@ -9509,8 +13666,27 @@
       <c r="M218">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O218">
+        <v>-2.5499999999999998</v>
+      </c>
+      <c r="P218">
+        <v>-2.5746961079210799</v>
+      </c>
+      <c r="Q218">
+        <v>-2.2600878424359898</v>
+      </c>
+      <c r="R218">
+        <v>-2.2195550030637299</v>
+      </c>
+      <c r="S218">
+        <v>2.2195550030637299</v>
+      </c>
+      <c r="T218" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>239</v>
       </c>
@@ -9550,8 +13726,27 @@
       <c r="M219">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O219">
+        <v>0</v>
+      </c>
+      <c r="P219">
+        <v>0</v>
+      </c>
+      <c r="Q219">
+        <v>0</v>
+      </c>
+      <c r="R219">
+        <v>0</v>
+      </c>
+      <c r="S219">
+        <v>0</v>
+      </c>
+      <c r="T219" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>240</v>
       </c>
@@ -9591,8 +13786,27 @@
       <c r="M220">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O220">
+        <v>0</v>
+      </c>
+      <c r="P220">
+        <v>0</v>
+      </c>
+      <c r="Q220">
+        <v>0</v>
+      </c>
+      <c r="R220">
+        <v>0</v>
+      </c>
+      <c r="S220">
+        <v>0</v>
+      </c>
+      <c r="T220" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>241</v>
       </c>
@@ -9632,8 +13846,27 @@
       <c r="M221">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O221">
+        <v>0</v>
+      </c>
+      <c r="P221">
+        <v>0</v>
+      </c>
+      <c r="Q221">
+        <v>0</v>
+      </c>
+      <c r="R221">
+        <v>0</v>
+      </c>
+      <c r="S221">
+        <v>0</v>
+      </c>
+      <c r="T221" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>242</v>
       </c>
@@ -9673,8 +13906,27 @@
       <c r="M222">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O222">
+        <v>0</v>
+      </c>
+      <c r="P222">
+        <v>0</v>
+      </c>
+      <c r="Q222">
+        <v>0</v>
+      </c>
+      <c r="R222">
+        <v>0</v>
+      </c>
+      <c r="S222">
+        <v>0</v>
+      </c>
+      <c r="T222" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>243</v>
       </c>
@@ -9714,8 +13966,27 @@
       <c r="M223">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O223">
+        <v>-0.08</v>
+      </c>
+      <c r="P223">
+        <v>-7.7851153506142495E-2</v>
+      </c>
+      <c r="Q223">
+        <v>-7.6801700079792604E-2</v>
+      </c>
+      <c r="R223">
+        <v>-6.4008227218612004E-2</v>
+      </c>
+      <c r="S223">
+        <v>6.4008227218612004E-2</v>
+      </c>
+      <c r="T223" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>244</v>
       </c>
@@ -9755,8 +14026,27 @@
       <c r="M224">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O224">
+        <v>0</v>
+      </c>
+      <c r="P224">
+        <v>0</v>
+      </c>
+      <c r="Q224">
+        <v>0</v>
+      </c>
+      <c r="R224">
+        <v>0</v>
+      </c>
+      <c r="S224">
+        <v>0</v>
+      </c>
+      <c r="T224" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>245</v>
       </c>
@@ -9796,8 +14086,27 @@
       <c r="M225">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O225">
+        <v>-0.61</v>
+      </c>
+      <c r="P225">
+        <v>-0.63680677882117898</v>
+      </c>
+      <c r="Q225">
+        <v>-0.58941484970798697</v>
+      </c>
+      <c r="R225">
+        <v>-0.58551024880949598</v>
+      </c>
+      <c r="S225">
+        <v>0.58551024880949598</v>
+      </c>
+      <c r="T225" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>246</v>
       </c>
@@ -9837,8 +14146,27 @@
       <c r="M226">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O226">
+        <v>-0.77</v>
+      </c>
+      <c r="P226">
+        <v>-0.77074325672479305</v>
+      </c>
+      <c r="Q226">
+        <v>-0.68334160064701899</v>
+      </c>
+      <c r="R226">
+        <v>-0.68709513858849602</v>
+      </c>
+      <c r="S226">
+        <v>0.68709513858849602</v>
+      </c>
+      <c r="T226" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>247</v>
       </c>
@@ -9878,8 +14206,27 @@
       <c r="M227">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O227">
+        <v>-0.61</v>
+      </c>
+      <c r="P227">
+        <v>-0.68597154481965705</v>
+      </c>
+      <c r="Q227">
+        <v>-0.56999044320157399</v>
+      </c>
+      <c r="R227">
+        <v>-0.56937331770811395</v>
+      </c>
+      <c r="S227">
+        <v>0.56937331770811395</v>
+      </c>
+      <c r="T227" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>248</v>
       </c>
@@ -9919,8 +14266,27 @@
       <c r="M228">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O228">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="P228">
+        <v>-0.31087025137884999</v>
+      </c>
+      <c r="Q228">
+        <v>-0.268518982532923</v>
+      </c>
+      <c r="R228">
+        <v>-0.264833548096224</v>
+      </c>
+      <c r="S228">
+        <v>0.264833548096224</v>
+      </c>
+      <c r="T228" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>249</v>
       </c>
@@ -9960,8 +14326,27 @@
       <c r="M229">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O229">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="P229">
+        <v>-0.30861942626626898</v>
+      </c>
+      <c r="Q229">
+        <v>-0.286091529792946</v>
+      </c>
+      <c r="R229">
+        <v>-0.24564462443343399</v>
+      </c>
+      <c r="S229">
+        <v>0.24564462443343399</v>
+      </c>
+      <c r="T229" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>250</v>
       </c>
@@ -10001,8 +14386,27 @@
       <c r="M230">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O230">
+        <v>0.23</v>
+      </c>
+      <c r="P230">
+        <v>0.21077015430064899</v>
+      </c>
+      <c r="Q230">
+        <v>0.22329992733915199</v>
+      </c>
+      <c r="R230">
+        <v>0.20516347691790199</v>
+      </c>
+      <c r="S230">
+        <v>-0.20516347691790199</v>
+      </c>
+      <c r="T230" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>281</v>
       </c>
@@ -10042,8 +14446,27 @@
       <c r="M231">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O231">
+        <v>0.33100000000000002</v>
+      </c>
+      <c r="P231">
+        <v>0.35121845264421497</v>
+      </c>
+      <c r="Q231">
+        <v>0.33270300232813599</v>
+      </c>
+      <c r="R231">
+        <v>0.29039102955921497</v>
+      </c>
+      <c r="S231">
+        <v>-0.29039102955921497</v>
+      </c>
+      <c r="T231" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>319</v>
       </c>
@@ -10083,8 +14506,27 @@
       <c r="M232">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O232">
+        <v>-1.1579999999999999</v>
+      </c>
+      <c r="P232">
+        <v>-1.0832603621388099</v>
+      </c>
+      <c r="Q232">
+        <v>-1.06872677259556</v>
+      </c>
+      <c r="R232">
+        <v>-1.1050951719632001</v>
+      </c>
+      <c r="S232">
+        <v>1.1050951719632001</v>
+      </c>
+      <c r="T232" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>320</v>
       </c>
@@ -10124,8 +14566,27 @@
       <c r="M233">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O233">
+        <v>-2.4E-2</v>
+      </c>
+      <c r="P233">
+        <v>-2.6124584047055199E-2</v>
+      </c>
+      <c r="Q233">
+        <v>-2.2076575589668E-2</v>
+      </c>
+      <c r="R233">
+        <v>-2.1215021961624999E-2</v>
+      </c>
+      <c r="S233">
+        <v>2.1215021961624999E-2</v>
+      </c>
+      <c r="T233" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>322</v>
       </c>
@@ -10165,8 +14626,27 @@
       <c r="M234">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O234">
+        <v>-2.4E-2</v>
+      </c>
+      <c r="P234">
+        <v>-2.35095190366638E-2</v>
+      </c>
+      <c r="Q234">
+        <v>-2.20310624586205E-2</v>
+      </c>
+      <c r="R234">
+        <v>-2.1292006294182798E-2</v>
+      </c>
+      <c r="S234">
+        <v>2.1292006294182798E-2</v>
+      </c>
+      <c r="T234" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>323</v>
       </c>
@@ -10206,8 +14686,27 @@
       <c r="M235">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O235">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="P235">
+        <v>0.15766416426479099</v>
+      </c>
+      <c r="Q235">
+        <v>0.140632885923728</v>
+      </c>
+      <c r="R235">
+        <v>0.12745943162578999</v>
+      </c>
+      <c r="S235">
+        <v>-0.12745943162578999</v>
+      </c>
+      <c r="T235" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>324</v>
       </c>
@@ -10247,8 +14746,27 @@
       <c r="M236">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O236">
+        <v>-0.247</v>
+      </c>
+      <c r="P236">
+        <v>-0.25746515954531002</v>
+      </c>
+      <c r="Q236">
+        <v>-0.202435881670017</v>
+      </c>
+      <c r="R236">
+        <v>-0.22220317706831499</v>
+      </c>
+      <c r="S236">
+        <v>0.22220317706831499</v>
+      </c>
+      <c r="T236" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>526</v>
       </c>
@@ -10288,8 +14806,27 @@
       <c r="M237">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O237">
+        <v>-1.4530000000000001</v>
+      </c>
+      <c r="P237">
+        <v>-1.4344591912506801</v>
+      </c>
+      <c r="Q237">
+        <v>-1.4132120739171199</v>
+      </c>
+      <c r="R237">
+        <v>-1.2983825881062401</v>
+      </c>
+      <c r="S237">
+        <v>1.2983825881062401</v>
+      </c>
+      <c r="T237" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>528</v>
       </c>
@@ -10329,8 +14866,27 @@
       <c r="M238">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O238">
+        <v>-0.28100000000000003</v>
+      </c>
+      <c r="P238">
+        <v>-0.295544366590478</v>
+      </c>
+      <c r="Q238">
+        <v>-0.26740120655989502</v>
+      </c>
+      <c r="R238">
+        <v>-0.24467923888757101</v>
+      </c>
+      <c r="S238">
+        <v>0.24467923888757101</v>
+      </c>
+      <c r="T238" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>531</v>
       </c>
@@ -10370,8 +14926,27 @@
       <c r="M239">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O239">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="P239">
+        <v>-0.135639857303364</v>
+      </c>
+      <c r="Q239">
+        <v>-0.13593735105785201</v>
+      </c>
+      <c r="R239">
+        <v>-0.121413694275104</v>
+      </c>
+      <c r="S239">
+        <v>0.121413694275104</v>
+      </c>
+      <c r="T239" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>552</v>
       </c>
@@ -10411,8 +14986,27 @@
       <c r="M240">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O240">
+        <v>0.111</v>
+      </c>
+      <c r="P240">
+        <v>0.11165291286535201</v>
+      </c>
+      <c r="Q240">
+        <v>9.9242912169252198E-2</v>
+      </c>
+      <c r="R240">
+        <v>9.8248911421926197E-2</v>
+      </c>
+      <c r="S240">
+        <v>-9.8248911421926197E-2</v>
+      </c>
+      <c r="T240" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>562</v>
       </c>
@@ -10452,8 +15046,27 @@
       <c r="M241">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O241">
+        <v>-0.505</v>
+      </c>
+      <c r="P241">
+        <v>-0.51476662171363596</v>
+      </c>
+      <c r="Q241">
+        <v>-0.46412602860062702</v>
+      </c>
+      <c r="R241">
+        <v>-0.41353088034860402</v>
+      </c>
+      <c r="S241">
+        <v>0.41353088034860402</v>
+      </c>
+      <c r="T241" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>609</v>
       </c>
@@ -10493,8 +15106,27 @@
       <c r="M242">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O242">
+        <v>-0.29599999999999999</v>
+      </c>
+      <c r="P242">
+        <v>-0.317796438508196</v>
+      </c>
+      <c r="Q242">
+        <v>-0.263002291761882</v>
+      </c>
+      <c r="R242">
+        <v>-0.25314829749673201</v>
+      </c>
+      <c r="S242">
+        <v>0.25314829749673201</v>
+      </c>
+      <c r="T242" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>664</v>
       </c>
@@ -10534,8 +15166,27 @@
       <c r="M243">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O243">
+        <v>1.137</v>
+      </c>
+      <c r="P243">
+        <v>1.1921003994372501</v>
+      </c>
+      <c r="Q243">
+        <v>0.95116223204786798</v>
+      </c>
+      <c r="R243">
+        <v>0.964560170589711</v>
+      </c>
+      <c r="S243">
+        <v>-0.964560170589711</v>
+      </c>
+      <c r="T243" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>1190</v>
       </c>
@@ -10575,8 +15226,27 @@
       <c r="M244">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O244">
+        <v>-1.0031000000000001</v>
+      </c>
+      <c r="P244">
+        <v>-1.01745338393056</v>
+      </c>
+      <c r="Q244">
+        <v>-0.84957315604569505</v>
+      </c>
+      <c r="R244">
+        <v>-0.90095650919212</v>
+      </c>
+      <c r="S244">
+        <v>0.90095650919212</v>
+      </c>
+      <c r="T244" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>1200</v>
       </c>
@@ -10616,8 +15286,27 @@
       <c r="M245">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O245">
+        <v>1</v>
+      </c>
+      <c r="P245">
+        <v>0.90317653454092195</v>
+      </c>
+      <c r="Q245">
+        <v>0.92059476149296804</v>
+      </c>
+      <c r="R245">
+        <v>0.82813873263966697</v>
+      </c>
+      <c r="S245">
+        <v>-0.82813873263966697</v>
+      </c>
+      <c r="T245" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>1201</v>
       </c>
@@ -10657,8 +15346,27 @@
       <c r="M246">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O246">
+        <v>0</v>
+      </c>
+      <c r="P246">
+        <v>0</v>
+      </c>
+      <c r="Q246">
+        <v>0</v>
+      </c>
+      <c r="R246">
+        <v>0</v>
+      </c>
+      <c r="S246">
+        <v>0</v>
+      </c>
+      <c r="T246" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>2040</v>
       </c>
@@ -10698,8 +15406,27 @@
       <c r="M247">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O247">
+        <v>0</v>
+      </c>
+      <c r="P247">
+        <v>0</v>
+      </c>
+      <c r="Q247">
+        <v>0</v>
+      </c>
+      <c r="R247">
+        <v>0</v>
+      </c>
+      <c r="S247">
+        <v>0</v>
+      </c>
+      <c r="T247" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>7001</v>
       </c>
@@ -10739,8 +15466,27 @@
       <c r="M248">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O248">
+        <v>0</v>
+      </c>
+      <c r="P248">
+        <v>0</v>
+      </c>
+      <c r="Q248">
+        <v>0</v>
+      </c>
+      <c r="R248">
+        <v>0</v>
+      </c>
+      <c r="S248">
+        <v>0</v>
+      </c>
+      <c r="T248" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>7002</v>
       </c>
@@ -10780,8 +15526,27 @@
       <c r="M249">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O249">
+        <v>0</v>
+      </c>
+      <c r="P249">
+        <v>0</v>
+      </c>
+      <c r="Q249">
+        <v>0</v>
+      </c>
+      <c r="R249">
+        <v>0</v>
+      </c>
+      <c r="S249">
+        <v>0</v>
+      </c>
+      <c r="T249" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>7003</v>
       </c>
@@ -10821,8 +15586,27 @@
       <c r="M250">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O250">
+        <v>0</v>
+      </c>
+      <c r="P250">
+        <v>0</v>
+      </c>
+      <c r="Q250">
+        <v>0</v>
+      </c>
+      <c r="R250">
+        <v>0</v>
+      </c>
+      <c r="S250">
+        <v>0</v>
+      </c>
+      <c r="T250" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>7011</v>
       </c>
@@ -10862,8 +15646,27 @@
       <c r="M251">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O251">
+        <v>0</v>
+      </c>
+      <c r="P251">
+        <v>0</v>
+      </c>
+      <c r="Q251">
+        <v>0</v>
+      </c>
+      <c r="R251">
+        <v>0</v>
+      </c>
+      <c r="S251">
+        <v>0</v>
+      </c>
+      <c r="T251" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>7012</v>
       </c>
@@ -10903,8 +15706,27 @@
       <c r="M252">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O252">
+        <v>0</v>
+      </c>
+      <c r="P252">
+        <v>0</v>
+      </c>
+      <c r="Q252">
+        <v>0</v>
+      </c>
+      <c r="R252">
+        <v>0</v>
+      </c>
+      <c r="S252">
+        <v>0</v>
+      </c>
+      <c r="T252" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>7017</v>
       </c>
@@ -10944,8 +15766,27 @@
       <c r="M253">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O253">
+        <v>0</v>
+      </c>
+      <c r="P253">
+        <v>0</v>
+      </c>
+      <c r="Q253">
+        <v>0</v>
+      </c>
+      <c r="R253">
+        <v>0</v>
+      </c>
+      <c r="S253">
+        <v>0</v>
+      </c>
+      <c r="T253" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>7023</v>
       </c>
@@ -10985,8 +15826,27 @@
       <c r="M254">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O254">
+        <v>0</v>
+      </c>
+      <c r="P254">
+        <v>0</v>
+      </c>
+      <c r="Q254">
+        <v>0</v>
+      </c>
+      <c r="R254">
+        <v>0</v>
+      </c>
+      <c r="S254">
+        <v>0</v>
+      </c>
+      <c r="T254" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>7024</v>
       </c>
@@ -11026,8 +15886,27 @@
       <c r="M255">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O255">
+        <v>0</v>
+      </c>
+      <c r="P255">
+        <v>0</v>
+      </c>
+      <c r="Q255">
+        <v>0</v>
+      </c>
+      <c r="R255">
+        <v>0</v>
+      </c>
+      <c r="S255">
+        <v>0</v>
+      </c>
+      <c r="T255" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>7039</v>
       </c>
@@ -11067,8 +15946,27 @@
       <c r="M256">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O256">
+        <v>0</v>
+      </c>
+      <c r="P256">
+        <v>0</v>
+      </c>
+      <c r="Q256">
+        <v>0</v>
+      </c>
+      <c r="R256">
+        <v>0</v>
+      </c>
+      <c r="S256">
+        <v>0</v>
+      </c>
+      <c r="T256" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>7044</v>
       </c>
@@ -11108,8 +16006,27 @@
       <c r="M257">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O257">
+        <v>0</v>
+      </c>
+      <c r="P257">
+        <v>0</v>
+      </c>
+      <c r="Q257">
+        <v>0</v>
+      </c>
+      <c r="R257">
+        <v>0</v>
+      </c>
+      <c r="S257">
+        <v>0</v>
+      </c>
+      <c r="T257" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>7049</v>
       </c>
@@ -11149,8 +16066,27 @@
       <c r="M258">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O258">
+        <v>0</v>
+      </c>
+      <c r="P258">
+        <v>0</v>
+      </c>
+      <c r="Q258">
+        <v>0</v>
+      </c>
+      <c r="R258">
+        <v>0</v>
+      </c>
+      <c r="S258">
+        <v>0</v>
+      </c>
+      <c r="T258" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>7055</v>
       </c>
@@ -11190,8 +16126,27 @@
       <c r="M259">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O259">
+        <v>0</v>
+      </c>
+      <c r="P259">
+        <v>0</v>
+      </c>
+      <c r="Q259">
+        <v>0</v>
+      </c>
+      <c r="R259">
+        <v>0</v>
+      </c>
+      <c r="S259">
+        <v>0</v>
+      </c>
+      <c r="T259" t="b">
+        <f t="shared" ref="T259:T301" si="4">R259=-S259</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>7057</v>
       </c>
@@ -11231,8 +16186,27 @@
       <c r="M260">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O260">
+        <v>0</v>
+      </c>
+      <c r="P260">
+        <v>0</v>
+      </c>
+      <c r="Q260">
+        <v>0</v>
+      </c>
+      <c r="R260">
+        <v>0</v>
+      </c>
+      <c r="S260">
+        <v>0</v>
+      </c>
+      <c r="T260" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>7061</v>
       </c>
@@ -11272,8 +16246,27 @@
       <c r="M261">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O261">
+        <v>0</v>
+      </c>
+      <c r="P261">
+        <v>0</v>
+      </c>
+      <c r="Q261">
+        <v>0</v>
+      </c>
+      <c r="R261">
+        <v>0</v>
+      </c>
+      <c r="S261">
+        <v>0</v>
+      </c>
+      <c r="T261" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>7062</v>
       </c>
@@ -11313,8 +16306,27 @@
       <c r="M262">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O262">
+        <v>0</v>
+      </c>
+      <c r="P262">
+        <v>0</v>
+      </c>
+      <c r="Q262">
+        <v>0</v>
+      </c>
+      <c r="R262">
+        <v>0</v>
+      </c>
+      <c r="S262">
+        <v>0</v>
+      </c>
+      <c r="T262" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>7071</v>
       </c>
@@ -11354,8 +16366,27 @@
       <c r="M263">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O263">
+        <v>0</v>
+      </c>
+      <c r="P263">
+        <v>0</v>
+      </c>
+      <c r="Q263">
+        <v>0</v>
+      </c>
+      <c r="R263">
+        <v>0</v>
+      </c>
+      <c r="S263">
+        <v>0</v>
+      </c>
+      <c r="T263" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>7130</v>
       </c>
@@ -11395,8 +16426,27 @@
       <c r="M264">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O264">
+        <v>0</v>
+      </c>
+      <c r="P264">
+        <v>0</v>
+      </c>
+      <c r="Q264">
+        <v>0</v>
+      </c>
+      <c r="R264">
+        <v>0</v>
+      </c>
+      <c r="S264">
+        <v>0</v>
+      </c>
+      <c r="T264" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>7139</v>
       </c>
@@ -11436,8 +16486,27 @@
       <c r="M265">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O265">
+        <v>0</v>
+      </c>
+      <c r="P265">
+        <v>0</v>
+      </c>
+      <c r="Q265">
+        <v>0</v>
+      </c>
+      <c r="R265">
+        <v>0</v>
+      </c>
+      <c r="S265">
+        <v>0</v>
+      </c>
+      <c r="T265" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>7166</v>
       </c>
@@ -11477,8 +16546,27 @@
       <c r="M266">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O266">
+        <v>0</v>
+      </c>
+      <c r="P266">
+        <v>0</v>
+      </c>
+      <c r="Q266">
+        <v>0</v>
+      </c>
+      <c r="R266">
+        <v>0</v>
+      </c>
+      <c r="S266">
+        <v>0</v>
+      </c>
+      <c r="T266" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>9001</v>
       </c>
@@ -11518,8 +16606,27 @@
       <c r="M267">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O267">
+        <v>0</v>
+      </c>
+      <c r="P267">
+        <v>0</v>
+      </c>
+      <c r="Q267">
+        <v>0</v>
+      </c>
+      <c r="R267">
+        <v>0</v>
+      </c>
+      <c r="S267">
+        <v>0</v>
+      </c>
+      <c r="T267" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>9002</v>
       </c>
@@ -11559,8 +16666,27 @@
       <c r="M268">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O268">
+        <v>-4.2000000000000003E-2</v>
+      </c>
+      <c r="P268">
+        <v>-3.95895317512528E-2</v>
+      </c>
+      <c r="Q268">
+        <v>-3.4362320187315699E-2</v>
+      </c>
+      <c r="R268">
+        <v>-3.7601323724026199E-2</v>
+      </c>
+      <c r="S268">
+        <v>3.7601323724026199E-2</v>
+      </c>
+      <c r="T268" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>9003</v>
       </c>
@@ -11600,8 +16726,27 @@
       <c r="M269">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O269">
+        <v>-2.7099999999999999E-2</v>
+      </c>
+      <c r="P269">
+        <v>-2.8969047763041499E-2</v>
+      </c>
+      <c r="Q269">
+        <v>-2.3702784732796502E-2</v>
+      </c>
+      <c r="R269">
+        <v>-2.4251749521315299E-2</v>
+      </c>
+      <c r="S269">
+        <v>2.4251749521315299E-2</v>
+      </c>
+      <c r="T269" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>9004</v>
       </c>
@@ -11641,8 +16786,27 @@
       <c r="M270">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O270">
+        <v>-8.6E-3</v>
+      </c>
+      <c r="P270">
+        <v>-8.0492179887211995E-3</v>
+      </c>
+      <c r="Q270">
+        <v>-8.2119454362056393E-3</v>
+      </c>
+      <c r="R270">
+        <v>-7.7921670513872703E-3</v>
+      </c>
+      <c r="S270">
+        <v>7.7921670513872703E-3</v>
+      </c>
+      <c r="T270" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>9005</v>
       </c>
@@ -11682,8 +16846,27 @@
       <c r="M271">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O271">
+        <v>0</v>
+      </c>
+      <c r="P271">
+        <v>0</v>
+      </c>
+      <c r="Q271">
+        <v>0</v>
+      </c>
+      <c r="R271">
+        <v>0</v>
+      </c>
+      <c r="S271">
+        <v>0</v>
+      </c>
+      <c r="T271" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>9006</v>
       </c>
@@ -11723,8 +16906,27 @@
       <c r="M272">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O272">
+        <v>0</v>
+      </c>
+      <c r="P272">
+        <v>0</v>
+      </c>
+      <c r="Q272">
+        <v>0</v>
+      </c>
+      <c r="R272">
+        <v>0</v>
+      </c>
+      <c r="S272">
+        <v>0</v>
+      </c>
+      <c r="T272" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>9007</v>
       </c>
@@ -11764,8 +16966,27 @@
       <c r="M273">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O273">
+        <v>0</v>
+      </c>
+      <c r="P273">
+        <v>0</v>
+      </c>
+      <c r="Q273">
+        <v>0</v>
+      </c>
+      <c r="R273">
+        <v>0</v>
+      </c>
+      <c r="S273">
+        <v>0</v>
+      </c>
+      <c r="T273" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>9012</v>
       </c>
@@ -11805,8 +17026,27 @@
       <c r="M274">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O274">
+        <v>0</v>
+      </c>
+      <c r="P274">
+        <v>0</v>
+      </c>
+      <c r="Q274">
+        <v>0</v>
+      </c>
+      <c r="R274">
+        <v>0</v>
+      </c>
+      <c r="S274">
+        <v>0</v>
+      </c>
+      <c r="T274" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>9021</v>
       </c>
@@ -11846,8 +17086,27 @@
       <c r="M275">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O275">
+        <v>-4.7500000000000001E-2</v>
+      </c>
+      <c r="P275">
+        <v>-4.8980773082555898E-2</v>
+      </c>
+      <c r="Q275">
+        <v>-4.1644813402716099E-2</v>
+      </c>
+      <c r="R275">
+        <v>-4.4511057701168699E-2</v>
+      </c>
+      <c r="S275">
+        <v>4.4511057701168699E-2</v>
+      </c>
+      <c r="T275" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>9022</v>
       </c>
@@ -11887,8 +17146,27 @@
       <c r="M276">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O276">
+        <v>-1.5299999999999999E-2</v>
+      </c>
+      <c r="P276">
+        <v>-1.6230234980853402E-2</v>
+      </c>
+      <c r="Q276">
+        <v>-1.38893522190451E-2</v>
+      </c>
+      <c r="R276">
+        <v>-1.30301241714188E-2</v>
+      </c>
+      <c r="S276">
+        <v>1.30301241714188E-2</v>
+      </c>
+      <c r="T276" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>9023</v>
       </c>
@@ -11928,8 +17206,27 @@
       <c r="M277">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O277">
+        <v>0</v>
+      </c>
+      <c r="P277">
+        <v>0</v>
+      </c>
+      <c r="Q277">
+        <v>0</v>
+      </c>
+      <c r="R277">
+        <v>0</v>
+      </c>
+      <c r="S277">
+        <v>0</v>
+      </c>
+      <c r="T277" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>9024</v>
       </c>
@@ -11969,8 +17266,27 @@
       <c r="M278">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O278">
+        <v>-1.35E-2</v>
+      </c>
+      <c r="P278">
+        <v>-1.3803527238186701E-2</v>
+      </c>
+      <c r="Q278">
+        <v>-1.28850110581717E-2</v>
+      </c>
+      <c r="R278">
+        <v>-1.23151804916511E-2</v>
+      </c>
+      <c r="S278">
+        <v>1.23151804916511E-2</v>
+      </c>
+      <c r="T278" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>9025</v>
       </c>
@@ -12010,8 +17326,27 @@
       <c r="M279">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O279">
+        <v>-4.4999999999999997E-3</v>
+      </c>
+      <c r="P279">
+        <v>-4.2013986663563896E-3</v>
+      </c>
+      <c r="Q279">
+        <v>-4.5766519681947901E-3</v>
+      </c>
+      <c r="R279">
+        <v>-3.84084133379779E-3</v>
+      </c>
+      <c r="S279">
+        <v>3.84084133379779E-3</v>
+      </c>
+      <c r="T279" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>9026</v>
       </c>
@@ -12051,8 +17386,27 @@
       <c r="M280">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O280">
+        <v>-4.4999999999999997E-3</v>
+      </c>
+      <c r="P280">
+        <v>-5.1014883261743301E-3</v>
+      </c>
+      <c r="Q280">
+        <v>-4.2062490283061599E-3</v>
+      </c>
+      <c r="R280">
+        <v>-3.85403616107519E-3</v>
+      </c>
+      <c r="S280">
+        <v>3.85403616107519E-3</v>
+      </c>
+      <c r="T280" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>9031</v>
       </c>
@@ -12092,8 +17446,27 @@
       <c r="M281">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O281">
+        <v>-1.84E-2</v>
+      </c>
+      <c r="P281">
+        <v>-1.88099427815333E-2</v>
+      </c>
+      <c r="Q281">
+        <v>-1.6523971412317699E-2</v>
+      </c>
+      <c r="R281">
+        <v>-1.66951387079852E-2</v>
+      </c>
+      <c r="S281">
+        <v>1.66951387079852E-2</v>
+      </c>
+      <c r="T281" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>9032</v>
       </c>
@@ -12133,8 +17506,27 @@
       <c r="M282">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O282">
+        <v>-1.3899999999999999E-2</v>
+      </c>
+      <c r="P282">
+        <v>-1.42660673707459E-2</v>
+      </c>
+      <c r="Q282">
+        <v>-1.30386114122406E-2</v>
+      </c>
+      <c r="R282">
+        <v>-1.2079619352693E-2</v>
+      </c>
+      <c r="S282">
+        <v>1.2079619352693E-2</v>
+      </c>
+      <c r="T282" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>9033</v>
       </c>
@@ -12174,8 +17566,27 @@
       <c r="M283">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O283">
+        <v>-1.89E-2</v>
+      </c>
+      <c r="P283">
+        <v>-1.9733280125967902E-2</v>
+      </c>
+      <c r="Q283">
+        <v>-1.80305414885365E-2</v>
+      </c>
+      <c r="R283">
+        <v>-1.7926153297011499E-2</v>
+      </c>
+      <c r="S283">
+        <v>1.7926153297011499E-2</v>
+      </c>
+      <c r="T283" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>9034</v>
       </c>
@@ -12215,8 +17626,27 @@
       <c r="M284">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O284">
+        <v>-1.55E-2</v>
+      </c>
+      <c r="P284">
+        <v>-1.5793695775840399E-2</v>
+      </c>
+      <c r="Q284">
+        <v>-1.4804385659613801E-2</v>
+      </c>
+      <c r="R284">
+        <v>-1.3631028927484299E-2</v>
+      </c>
+      <c r="S284">
+        <v>1.3631028927484299E-2</v>
+      </c>
+      <c r="T284" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>9035</v>
       </c>
@@ -12256,8 +17686,27 @@
       <c r="M285">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O285">
+        <v>-1.66E-2</v>
+      </c>
+      <c r="P285">
+        <v>-1.65822892883223E-2</v>
+      </c>
+      <c r="Q285">
+        <v>-1.4311594208967601E-2</v>
+      </c>
+      <c r="R285">
+        <v>-1.5480804059699701E-2</v>
+      </c>
+      <c r="S285">
+        <v>1.5480804059699701E-2</v>
+      </c>
+      <c r="T285" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>9036</v>
       </c>
@@ -12297,8 +17746,27 @@
       <c r="M286">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O286">
+        <v>-3.02999999999999E-2</v>
+      </c>
+      <c r="P286">
+        <v>-2.9629229800639201E-2</v>
+      </c>
+      <c r="Q286">
+        <v>-2.87958530754697E-2</v>
+      </c>
+      <c r="R286">
+        <v>-2.7018408273387601E-2</v>
+      </c>
+      <c r="S286">
+        <v>2.7018408273387601E-2</v>
+      </c>
+      <c r="T286" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>9037</v>
       </c>
@@ -12338,8 +17806,27 @@
       <c r="M287">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O287">
+        <v>-1.8599999999999998E-2</v>
+      </c>
+      <c r="P287">
+        <v>-1.85440433675521E-2</v>
+      </c>
+      <c r="Q287">
+        <v>-1.84602678869452E-2</v>
+      </c>
+      <c r="R287">
+        <v>-1.68387483311154E-2</v>
+      </c>
+      <c r="S287">
+        <v>1.68387483311154E-2</v>
+      </c>
+      <c r="T287" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>9038</v>
       </c>
@@ -12379,8 +17866,27 @@
       <c r="M288">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O288">
+        <v>-2.58E-2</v>
+      </c>
+      <c r="P288">
+        <v>-2.6497397413609899E-2</v>
+      </c>
+      <c r="Q288">
+        <v>-2.4670772808272699E-2</v>
+      </c>
+      <c r="R288">
+        <v>-2.2055319130730999E-2</v>
+      </c>
+      <c r="S288">
+        <v>2.2055319130730999E-2</v>
+      </c>
+      <c r="T288" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>9041</v>
       </c>
@@ -12420,8 +17926,27 @@
       <c r="M289">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O289">
+        <v>-1.01E-2</v>
+      </c>
+      <c r="P289">
+        <v>-1.0551556447654599E-2</v>
+      </c>
+      <c r="Q289">
+        <v>-9.6085937116848798E-3</v>
+      </c>
+      <c r="R289">
+        <v>-8.9618741995564303E-3</v>
+      </c>
+      <c r="S289">
+        <v>8.9618741995564303E-3</v>
+      </c>
+      <c r="T289" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>9042</v>
       </c>
@@ -12461,8 +17986,27 @@
       <c r="M290">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O290">
+        <v>-8.0999999999999996E-3</v>
+      </c>
+      <c r="P290">
+        <v>-8.1604927275765893E-3</v>
+      </c>
+      <c r="Q290">
+        <v>-8.0616915009905192E-3</v>
+      </c>
+      <c r="R290">
+        <v>-7.6128923679712503E-3</v>
+      </c>
+      <c r="S290">
+        <v>7.6128923679712503E-3</v>
+      </c>
+      <c r="T290" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>9043</v>
       </c>
@@ -12502,8 +18046,27 @@
       <c r="M291">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O291">
+        <v>-1.6E-2</v>
+      </c>
+      <c r="P291">
+        <v>-1.58408377046463E-2</v>
+      </c>
+      <c r="Q291">
+        <v>-1.5902746245415399E-2</v>
+      </c>
+      <c r="R291">
+        <v>-1.4738159661052999E-2</v>
+      </c>
+      <c r="S291">
+        <v>1.4738159661052999E-2</v>
+      </c>
+      <c r="T291" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>9044</v>
       </c>
@@ -12543,8 +18106,27 @@
       <c r="M292">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O292">
+        <v>0</v>
+      </c>
+      <c r="P292">
+        <v>0</v>
+      </c>
+      <c r="Q292">
+        <v>0</v>
+      </c>
+      <c r="R292">
+        <v>0</v>
+      </c>
+      <c r="S292">
+        <v>0</v>
+      </c>
+      <c r="T292" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>9051</v>
       </c>
@@ -12584,8 +18166,27 @@
       <c r="M293">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O293">
+        <v>-0.35809999999999997</v>
+      </c>
+      <c r="P293">
+        <v>-0.40720054574312697</v>
+      </c>
+      <c r="Q293">
+        <v>-0.356856671508615</v>
+      </c>
+      <c r="R293">
+        <v>-0.28982418203881499</v>
+      </c>
+      <c r="S293">
+        <v>0.28982418203881499</v>
+      </c>
+      <c r="T293" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>9052</v>
       </c>
@@ -12625,8 +18226,27 @@
       <c r="M294">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O294">
+        <v>-0.3</v>
+      </c>
+      <c r="P294">
+        <v>-0.34860308313358601</v>
+      </c>
+      <c r="Q294">
+        <v>-0.29245182697258798</v>
+      </c>
+      <c r="R294">
+        <v>-0.27694204741996098</v>
+      </c>
+      <c r="S294">
+        <v>0.27694204741996098</v>
+      </c>
+      <c r="T294" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>9053</v>
       </c>
@@ -12666,8 +18286,27 @@
       <c r="M295">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O295">
+        <v>-0.26479999999999998</v>
+      </c>
+      <c r="P295">
+        <v>-0.260203929954547</v>
+      </c>
+      <c r="Q295">
+        <v>-0.25653642992095599</v>
+      </c>
+      <c r="R295">
+        <v>-0.25091249656750297</v>
+      </c>
+      <c r="S295">
+        <v>0.25091249656750297</v>
+      </c>
+      <c r="T295" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>9054</v>
       </c>
@@ -12707,8 +18346,27 @@
       <c r="M296">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O296">
+        <v>0</v>
+      </c>
+      <c r="P296">
+        <v>0</v>
+      </c>
+      <c r="Q296">
+        <v>0</v>
+      </c>
+      <c r="R296">
+        <v>0</v>
+      </c>
+      <c r="S296">
+        <v>0</v>
+      </c>
+      <c r="T296" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>9055</v>
       </c>
@@ -12748,8 +18406,27 @@
       <c r="M297">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O297">
+        <v>0</v>
+      </c>
+      <c r="P297">
+        <v>0</v>
+      </c>
+      <c r="Q297">
+        <v>0</v>
+      </c>
+      <c r="R297">
+        <v>0</v>
+      </c>
+      <c r="S297">
+        <v>0</v>
+      </c>
+      <c r="T297" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>9071</v>
       </c>
@@ -12789,8 +18466,27 @@
       <c r="M298">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O298">
+        <v>-1.0200000000000001E-2</v>
+      </c>
+      <c r="P298">
+        <v>-9.4756666979381506E-3</v>
+      </c>
+      <c r="Q298">
+        <v>-9.3818505299046104E-3</v>
+      </c>
+      <c r="R298">
+        <v>-8.9485444031676704E-3</v>
+      </c>
+      <c r="S298">
+        <v>8.9485444031676704E-3</v>
+      </c>
+      <c r="T298" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>9072</v>
       </c>
@@ -12830,8 +18526,27 @@
       <c r="M299">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O299">
+        <v>-1.0200000000000001E-2</v>
+      </c>
+      <c r="P299">
+        <v>-1.04542721046933E-2</v>
+      </c>
+      <c r="Q299">
+        <v>-9.1491855269369097E-3</v>
+      </c>
+      <c r="R299">
+        <v>-8.4164923346858097E-3</v>
+      </c>
+      <c r="S299">
+        <v>8.4164923346858097E-3</v>
+      </c>
+      <c r="T299" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>9121</v>
       </c>
@@ -12871,8 +18586,27 @@
       <c r="M300">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O300">
+        <v>-3.7999999999999999E-2</v>
+      </c>
+      <c r="P300">
+        <v>-3.7401987453511101E-2</v>
+      </c>
+      <c r="Q300">
+        <v>-3.4153403887688998E-2</v>
+      </c>
+      <c r="R300">
+        <v>-3.4898320663287498E-2</v>
+      </c>
+      <c r="S300">
+        <v>3.4898320663287498E-2</v>
+      </c>
+      <c r="T300" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>9533</v>
       </c>
@@ -12912,8 +18646,31 @@
       <c r="M301">
         <v>0.94</v>
       </c>
+      <c r="O301">
+        <v>-1.18999999999999E-2</v>
+      </c>
+      <c r="P301">
+        <v>-1.1821673612297001E-2</v>
+      </c>
+      <c r="Q301">
+        <v>-1.0555572772419501E-2</v>
+      </c>
+      <c r="R301">
+        <v>-1.0630328386749901E-2</v>
+      </c>
+      <c r="S301">
+        <v>1.0630328386749901E-2</v>
+      </c>
+      <c r="T301" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="O2:T301" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <mergeCells count="1">
+    <mergeCell ref="P1:R1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17684,6 +23441,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:V70" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/excel_outputs/pglib_opf_case300_ieee.xlsx
+++ b/excel_outputs/pglib_opf_case300_ieee.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\firda\belajar\ISE711\excel_outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833D4D27-4694-4A11-80BC-53C198684F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0BDB0D-09B5-4E66-9967-9B012FAED76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="baseMVA" sheetId="1" r:id="rId1"/>
@@ -282,13 +282,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -657,11 +657,11 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
       <c r="S1" t="s">
         <v>54</v>
       </c>
@@ -718,7 +718,7 @@
       <c r="R2">
         <v>-0.81586728767348404</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="2">
         <v>0.81586728767348404</v>
       </c>
       <c r="T2" t="b">
@@ -18667,7 +18667,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="O2:T301" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="P1:R1"/>
   </mergeCells>
